--- a/VERGARA/Julio/vergara Julio.xlsx
+++ b/VERGARA/Julio/vergara Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4841E31-FE4C-486C-B7EE-597EFE05634E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BE57C4-FE47-4754-B4E0-318AD97F0B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="287">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>HORARIOS DE ATENCION: LUNES A VIERNES</t>
-  </si>
-  <si>
-    <t>VTO 14/07</t>
   </si>
   <si>
     <t>GASTOS ORDINARIOS UNIDADES FUNCIONALES:</t>
@@ -789,15 +786,6 @@
     <t>S.S.31</t>
   </si>
   <si>
-    <t>PERÍODO: JUNIO - ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
-  </si>
-  <si>
-    <t>Marcela De Biase-  Sra. Contadora - Mes de JUNIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JUNIO</t>
-  </si>
-  <si>
     <t>Transf 11/06</t>
   </si>
   <si>
@@ -816,9 +804,6 @@
     <t>Luz Maria Alberio</t>
   </si>
   <si>
-    <t>Honorarios administracion - Mes de MAYO Y JUNIO</t>
-  </si>
-  <si>
     <t>Transf 09/06</t>
   </si>
   <si>
@@ -840,9 +825,6 @@
     <t>Incluye SAC</t>
   </si>
   <si>
-    <t>Espindola Christian - Arreglo tuerca accionadora e instalacion rampa</t>
-  </si>
-  <si>
     <t>Tranfs 27/06</t>
   </si>
   <si>
@@ -852,12 +834,6 @@
     <t>Casa Ruan compra de materiales electricos</t>
   </si>
   <si>
-    <t xml:space="preserve">Doartero Julio - Emergencia falta de agua en tanques </t>
-  </si>
-  <si>
-    <t>Transf 27/06</t>
-  </si>
-  <si>
     <t>Transf 26/06</t>
   </si>
   <si>
@@ -886,6 +862,33 @@
   </si>
   <si>
     <t>Jose Luis urtibay pago cualquier cosa el tarado, no respeto decimales - Pago extraordinarias de muchas UFS</t>
+  </si>
+  <si>
+    <t>VTO 14/08</t>
+  </si>
+  <si>
+    <t>PERÍODO: JULIO - ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
+  </si>
+  <si>
+    <t>Marcela De Biase-  Sra. Contadora - Mes de JULIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JULIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mes de JUNIO Y JULIO</t>
+  </si>
+  <si>
+    <t>Transf 17/07</t>
+  </si>
+  <si>
+    <t>Servisur - Reemplazo 1 plafon psio 9 - 1 plafon sala de medidores - 3 lamparas salade gas</t>
+  </si>
+  <si>
+    <t>Transf 21/07</t>
+  </si>
+  <si>
+    <t>Casa ruan - compra de materiales</t>
   </si>
 </sst>
 </file>
@@ -893,15 +896,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1525,10 +1528,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1548,8 +1551,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1558,31 +1561,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1593,8 +1596,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1612,18 +1615,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1641,35 +1644,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1677,11 +1680,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1692,17 +1695,17 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1718,27 +1721,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1748,7 +1751,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1756,30 +1759,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1792,41 +1795,24 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1837,53 +1823,76 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2245,20 +2254,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="66" t="s">
         <v>0</v>
@@ -2267,7 +2276,7 @@
       <c r="D1" s="66"/>
       <c r="E1" s="67"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="130" t="s">
         <v>1</v>
@@ -2276,7 +2285,7 @@
       <c r="D2" s="130"/>
       <c r="E2" s="68"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
       <c r="B3" s="131" t="s">
         <v>2</v>
@@ -2287,7 +2296,7 @@
       </c>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2298,18 +2307,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="188" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="190"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="199" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="197"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="198"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2320,77 +2329,77 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="191" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="200" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="190"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="201" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="202"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="202"/>
+      <c r="B14" s="202"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="202"/>
+      <c r="B15" s="202"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="202"/>
+      <c r="B16" s="202"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="C8" s="192"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="192"/>
-      <c r="C9" s="192"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="192"/>
-      <c r="C10" s="192"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
-        <v>282</v>
-      </c>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
-      <c r="B16" s="194"/>
-      <c r="C16" s="194"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="194"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>10</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2398,12 +2407,12 @@
         <v>1033560</v>
       </c>
       <c r="E22" s="86" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2413,9 +2422,9 @@
       <c r="E23" s="86"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2425,9 +2434,9 @@
       <c r="E24" s="86"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="55"/>
       <c r="C25" s="55"/>
@@ -2438,9 +2447,9 @@
       <c r="E25" s="87"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -2451,45 +2460,45 @@
       </c>
       <c r="F26" s="19"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
       <c r="D27" s="33"/>
       <c r="E27" s="89"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="195" t="s">
-        <v>254</v>
-      </c>
-      <c r="B28" s="196"/>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="191" t="s">
+        <v>280</v>
+      </c>
+      <c r="B28" s="192"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="182">
+      <c r="D28" s="228">
         <v>35000</v>
       </c>
       <c r="E28" s="90" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="195" t="s">
-        <v>262</v>
-      </c>
-      <c r="B29" s="196"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="191" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="192"/>
       <c r="C29" s="5"/>
       <c r="D29" s="182">
         <f>470000*2</f>
         <v>940000</v>
       </c>
       <c r="E29" s="90" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
@@ -2499,18 +2508,18 @@
         <v>975000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="34"/>
       <c r="E31" s="65"/>
     </row>
-    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="154" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="148"/>
       <c r="C32" s="53"/>
@@ -2520,20 +2529,20 @@
       <c r="E32" s="113"/>
       <c r="G32" s="153"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="195" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="196"/>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="191" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="192"/>
       <c r="C33" s="53"/>
       <c r="D33" s="181">
         <v>719.9</v>
       </c>
       <c r="E33" s="113"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -2543,102 +2552,102 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
       <c r="D35" s="37"/>
       <c r="E35" s="93"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="52"/>
-      <c r="D36" s="184">
-        <v>297953.51</v>
+      <c r="D36" s="139">
+        <v>466260.75</v>
       </c>
       <c r="E36" s="115" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G36" s="120"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="181">
-        <v>26936.54</v>
+      <c r="D37" s="224">
+        <v>45243</v>
       </c>
       <c r="E37" s="101" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
         <f>A37</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="5"/>
-      <c r="D38" s="181">
-        <v>50908.49</v>
+      <c r="D38" s="224">
+        <v>83582.350000000006</v>
       </c>
       <c r="E38" s="101" t="str">
         <f>E37</f>
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
         <f>A38</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="181">
-        <v>2992.96</v>
+      <c r="D39" s="224">
+        <v>5027</v>
       </c>
       <c r="E39" s="102" t="str">
         <f>E37</f>
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
       <c r="D40" s="38"/>
       <c r="E40" s="92">
         <f>SUM(D36:D39)</f>
-        <v>378791.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>600113.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
       <c r="D41" s="37"/>
       <c r="E41" s="93"/>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="52"/>
       <c r="C42" s="52"/>
@@ -2647,12 +2656,12 @@
         <v>169258.92</v>
       </c>
       <c r="E42" s="99" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2660,25 +2669,25 @@
         <v>50000</v>
       </c>
       <c r="E43" s="99" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="195" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="196"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="191" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="192"/>
       <c r="C44" s="5"/>
       <c r="D44" s="181">
         <v>84984.35</v>
       </c>
       <c r="E44" s="99" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -2688,18 +2697,18 @@
         <v>304243.27</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="25"/>
       <c r="D46" s="36"/>
       <c r="E46" s="95"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="149" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B47" s="150"/>
       <c r="C47" s="63"/>
@@ -2707,51 +2716,51 @@
         <v>38950</v>
       </c>
       <c r="E47" s="151" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="195" t="s">
-        <v>272</v>
-      </c>
-      <c r="B48" s="196"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="191" t="s">
+        <v>266</v>
+      </c>
+      <c r="B48" s="192"/>
       <c r="C48" s="54"/>
       <c r="D48" s="181">
         <v>110000</v>
       </c>
       <c r="E48" s="151" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="201" t="s">
-        <v>257</v>
-      </c>
-      <c r="B49" s="202"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="194" t="s">
+        <v>253</v>
+      </c>
+      <c r="B49" s="195"/>
       <c r="C49" s="54"/>
       <c r="D49" s="181">
         <v>110000</v>
       </c>
       <c r="E49" s="151" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="195" t="s">
-        <v>260</v>
-      </c>
-      <c r="B50" s="196"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="191" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" s="192"/>
       <c r="C50" s="54"/>
       <c r="D50" s="181">
         <v>135000</v>
       </c>
       <c r="E50" s="151" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="137" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B51" s="126"/>
       <c r="C51" s="54"/>
@@ -2759,74 +2768,75 @@
         <v>25000</v>
       </c>
       <c r="E51" s="151" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="195" t="s">
-        <v>274</v>
-      </c>
-      <c r="B52" s="196"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="191" t="s">
+        <v>286</v>
+      </c>
+      <c r="B52" s="192"/>
       <c r="C52" s="54"/>
-      <c r="D52" s="181">
-        <v>150000</v>
+      <c r="D52" s="224">
+        <v>16500</v>
       </c>
       <c r="E52" s="152" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="198" t="s">
-        <v>270</v>
-      </c>
-      <c r="B53" s="199"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="222" t="s">
+        <v>284</v>
+      </c>
+      <c r="B53" s="223"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="181">
-        <v>110000</v>
+      <c r="D53" s="224">
+        <v>60000</v>
       </c>
       <c r="E53" s="152" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="195" t="s">
-        <v>259</v>
-      </c>
-      <c r="B54" s="196"/>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="191" t="s">
+        <v>255</v>
+      </c>
+      <c r="B54" s="192"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="97">
-        <v>51150</v>
-      </c>
-      <c r="E54" s="151" t="s">
-        <v>256</v>
-      </c>
-      <c r="I54" s="195"/>
-      <c r="J54" s="196"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D54" s="221">
+        <f>60650+58080</f>
+        <v>118730</v>
+      </c>
+      <c r="E54" s="225" t="s">
+        <v>283</v>
+      </c>
+      <c r="I54" s="191"/>
+      <c r="J54" s="192"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="32"/>
       <c r="D55" s="30"/>
       <c r="E55" s="147">
         <f>SUM(D47:D54)</f>
-        <v>730100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>614180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" s="64"/>
       <c r="C56" s="25"/>
       <c r="D56" s="27"/>
       <c r="E56" s="95"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2835,9 +2845,9 @@
       </c>
       <c r="E57" s="103"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2846,9 +2856,9 @@
       </c>
       <c r="E58" s="100"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B59" s="51"/>
       <c r="C59" s="51"/>
@@ -2858,81 +2868,81 @@
         <v>159752.69</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="86"/>
       <c r="E60" s="105"/>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" s="28"/>
       <c r="C61" s="28"/>
       <c r="D61" s="106"/>
       <c r="E61" s="136"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="D62" s="107"/>
       <c r="E62" s="108"/>
       <c r="F62" s="44"/>
       <c r="G62" s="143"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="4"/>
       <c r="D63" s="109"/>
       <c r="E63" s="135">
         <f>(SUM(E26:E61))</f>
-        <v>3428236.36</v>
+        <v>3533637.96</v>
       </c>
       <c r="F63" s="134"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D64" s="107"/>
       <c r="E64" s="107"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D65" s="107"/>
       <c r="E65" s="107"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="12"/>
       <c r="D66" s="110"/>
       <c r="E66" s="111"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="195" t="s">
-        <v>279</v>
-      </c>
-      <c r="B67" s="196"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="191" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="192"/>
       <c r="C67" s="5"/>
       <c r="D67" s="97">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
       <c r="E67" s="94" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="96"/>
       <c r="B68" s="98"/>
       <c r="C68" s="5"/>
       <c r="D68" s="97"/>
       <c r="E68" s="94"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="49"/>
       <c r="B69" s="48"/>
       <c r="C69" s="48"/>
@@ -2942,21 +2952,21 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="203" t="s">
+    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="196" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72" s="197"/>
+      <c r="C72" s="197"/>
+      <c r="D72" s="198"/>
+      <c r="E72" s="144"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B72" s="189"/>
-      <c r="C72" s="189"/>
-      <c r="D72" s="190"/>
-      <c r="E72" s="144"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="4"/>
@@ -2966,63 +2976,63 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B76" s="84">
         <f>E63</f>
-        <v>3428236.36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3533637.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" s="84">
         <f>E63-E61</f>
-        <v>3428236.36</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3533637.96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B78" s="84">
         <f>E74-E72</f>
         <v>609986.12</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="83" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B79" s="84">
         <f>E74</f>
         <v>609986.12</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B81" s="121"/>
       <c r="C81" s="20"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B82" s="57">
         <v>-408061.47</v>
       </c>
       <c r="C82" s="22"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B83" s="41">
         <f>PRORRATEO!H92</f>
@@ -3030,9 +3040,9 @@
       </c>
       <c r="C83" s="20"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B84" s="100">
         <f>B98</f>
@@ -3040,9 +3050,9 @@
       </c>
       <c r="C84" s="20"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="116" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B85" s="47">
         <f>-6174-2758</f>
@@ -3050,29 +3060,29 @@
       </c>
       <c r="C85" s="20"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B86" s="47">
         <f>-B77</f>
-        <v>-3428236.36</v>
+        <v>-3533637.96</v>
       </c>
       <c r="C86" s="20"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B87" s="47">
         <f>-PRORRATEO!F1</f>
-        <v>-1241030.1599999999</v>
+        <v>-2147076</v>
       </c>
       <c r="C87" s="20"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B88" s="47">
         <f>-PRORRATEO!F2</f>
@@ -3080,9 +3090,9 @@
       </c>
       <c r="C88" s="20"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B89" s="47">
         <f>-(B78)</f>
@@ -3090,65 +3100,65 @@
       </c>
       <c r="C89" s="20"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="124" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B90" s="125">
         <f>SUM(B82:B89)</f>
-        <v>831778.5099999985</v>
+        <v>-179668.93000000168</v>
       </c>
       <c r="C90" s="23"/>
       <c r="D90" s="44"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B91" s="42"/>
       <c r="C91" s="23"/>
       <c r="D91" s="44"/>
       <c r="E91" s="122"/>
       <c r="F91" s="123"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B92" s="42"/>
       <c r="C92" s="23"/>
       <c r="D92" s="44"/>
       <c r="E92" s="122"/>
       <c r="F92" s="123"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="200" t="s">
-        <v>58</v>
-      </c>
-      <c r="B93" s="192"/>
-      <c r="C93" s="192"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="192"/>
-      <c r="B94" s="192"/>
-      <c r="C94" s="192"/>
-    </row>
-    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="B93" s="190"/>
+      <c r="C93" s="190"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="190"/>
+      <c r="B94" s="190"/>
+      <c r="C94" s="190"/>
+    </row>
+    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
       <c r="B95" s="139"/>
       <c r="C95" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="53"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
     </row>
-    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="128"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B98" s="112">
         <f>SUM(B95:B97)</f>
@@ -3156,39 +3166,44 @@
       </c>
       <c r="C98" s="46"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="197"/>
-      <c r="B100" s="192"/>
-      <c r="C100" s="192"/>
-      <c r="D100" s="192"/>
-      <c r="E100" s="192"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="192"/>
-      <c r="B101" s="192"/>
-      <c r="C101" s="192"/>
-      <c r="D101" s="192"/>
-      <c r="E101" s="192"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="192"/>
-      <c r="B102" s="192"/>
-      <c r="C102" s="192"/>
-      <c r="D102" s="192"/>
-      <c r="E102" s="192"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="192"/>
-      <c r="B103" s="192"/>
-      <c r="C103" s="192"/>
-      <c r="D103" s="192"/>
-      <c r="E103" s="192"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="189"/>
+      <c r="B100" s="190"/>
+      <c r="C100" s="190"/>
+      <c r="D100" s="190"/>
+      <c r="E100" s="190"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="190"/>
+      <c r="B101" s="190"/>
+      <c r="C101" s="190"/>
+      <c r="D101" s="190"/>
+      <c r="E101" s="190"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="190"/>
+      <c r="B102" s="190"/>
+      <c r="C102" s="190"/>
+      <c r="D102" s="190"/>
+      <c r="E102" s="190"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="190"/>
+      <c r="B103" s="190"/>
+      <c r="C103" s="190"/>
+      <c r="D103" s="190"/>
+      <c r="E103" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="A52:B52"/>
@@ -3202,11 +3217,6 @@
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3217,174 +3227,174 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="226">
+        <v>2147076</v>
+      </c>
+      <c r="G1" s="227"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="185" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="209">
-        <v>1241030.1599999999</v>
-      </c>
-      <c r="G1" s="206"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="186" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="185"/>
-      <c r="M1" s="205">
+      <c r="L1" s="184"/>
+      <c r="M1" s="212">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="206"/>
+      <c r="N1" s="213"/>
       <c r="O1" s="138"/>
-      <c r="P1" s="204">
+      <c r="P1" s="211">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="192"/>
+      <c r="Q1" s="190"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="203">
+        <v>561462.80000000005</v>
+      </c>
+      <c r="G2" s="204"/>
+      <c r="H2" s="184" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="220">
-        <v>561462.80000000005</v>
-      </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="185" t="s">
+      <c r="I2" s="214">
+        <v>1200000</v>
+      </c>
+      <c r="J2" s="204"/>
+      <c r="K2" s="184" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="207">
-        <v>1200000</v>
-      </c>
-      <c r="J2" s="208"/>
-      <c r="K2" s="185" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" s="185"/>
-      <c r="M2" s="207">
+      <c r="L2" s="184"/>
+      <c r="M2" s="214">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
-      <c r="N2" s="208"/>
+      <c r="N2" s="204"/>
       <c r="O2" s="140"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="216"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="210" t="s">
+      <c r="P2" s="218"/>
+      <c r="Q2" s="219"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="215" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="117"/>
+      <c r="C3" s="205" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="217" t="s">
+      <c r="D3" s="205" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="217" t="s">
+      <c r="E3" s="210" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="222" t="s">
+      <c r="F3" s="205" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="217" t="s">
+      <c r="G3" s="207" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="212" t="s">
+      <c r="H3" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="217" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="217" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="214" t="s">
+      <c r="J3" s="207" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="212" t="s">
-        <v>71</v>
-      </c>
-      <c r="K3" s="221" t="str">
+      <c r="K3" s="209" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="212" t="s">
+      <c r="L3" s="207" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="207" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="212" t="s">
+      <c r="N3" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="212" t="s">
+      <c r="O3" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="212" t="s">
+      <c r="P3" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="Q3" s="220" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="219" t="s">
-        <v>77</v>
-      </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="211"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="216"/>
       <c r="B4" s="118"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/07</v>
-      </c>
-      <c r="Q4" s="218"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 14/08</v>
+      </c>
+      <c r="Q4" s="206"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="61"/>
       <c r="B5" s="61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" s="61">
         <v>33</v>
       </c>
       <c r="D5" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="61"/>
       <c r="F5" s="69">
@@ -3415,7 +3425,7 @@
       </c>
       <c r="M5" s="127">
         <f t="shared" ref="M5:M36" si="4">F$1*F5</f>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N5" s="127">
         <f t="shared" ref="N5:N36" si="5">F$2*F5</f>
@@ -3427,27 +3437,27 @@
       </c>
       <c r="P5" s="73">
         <f t="shared" ref="P5:P36" si="7">ROUND(SUM(I5:O5),0) + R5</f>
-        <v>145692.32999999999</v>
+        <v>163994.32999999999</v>
       </c>
       <c r="Q5" s="74">
         <f t="shared" ref="Q5:Q36" si="8">ROUND(P5*3%,0) + P5</f>
-        <v>150063.32999999999</v>
+        <v>168914.33</v>
       </c>
       <c r="R5" s="44">
         <f t="shared" ref="R5:R36" si="9">ROUND(0.001+C5/100,2)</f>
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="61"/>
       <c r="B6" s="61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="61">
         <v>34</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" s="62"/>
       <c r="F6" s="69">
@@ -3478,7 +3488,7 @@
       </c>
       <c r="M6" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N6" s="127">
         <f t="shared" si="5"/>
@@ -3490,11 +3500,11 @@
       </c>
       <c r="P6" s="73">
         <f t="shared" si="7"/>
-        <v>100253.34</v>
+        <v>112847.34</v>
       </c>
       <c r="Q6" s="74">
         <f t="shared" si="8"/>
-        <v>103261.34</v>
+        <v>116232.34</v>
       </c>
       <c r="R6" s="44">
         <f t="shared" si="9"/>
@@ -3502,18 +3512,18 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="61">
         <v>1</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="61">
         <v>35</v>
       </c>
       <c r="D7" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" s="75"/>
       <c r="F7" s="69">
@@ -3544,7 +3554,7 @@
       </c>
       <c r="M7" s="127">
         <f t="shared" si="4"/>
-        <v>17622.628271999998</v>
+        <v>30488.479200000002</v>
       </c>
       <c r="N7" s="127">
         <f t="shared" si="5"/>
@@ -3556,29 +3566,29 @@
       </c>
       <c r="P7" s="73">
         <f t="shared" si="7"/>
-        <v>96180.35</v>
+        <v>109046.35</v>
       </c>
       <c r="Q7" s="74">
         <f t="shared" si="8"/>
-        <v>99065.35</v>
+        <v>112317.35</v>
       </c>
       <c r="R7" s="44">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61">
         <v>2</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="61">
         <v>36</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="75"/>
       <c r="F8" s="69">
@@ -3609,7 +3619,7 @@
       </c>
       <c r="M8" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N8" s="127">
         <f t="shared" si="5"/>
@@ -3621,11 +3631,11 @@
       </c>
       <c r="P8" s="73">
         <f t="shared" si="7"/>
-        <v>136239.35999999999</v>
+        <v>154541.35999999999</v>
       </c>
       <c r="Q8" s="74">
         <f t="shared" si="8"/>
-        <v>140326.35999999999</v>
+        <v>159177.35999999999</v>
       </c>
       <c r="R8" s="44">
         <f t="shared" si="9"/>
@@ -3633,21 +3643,21 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="61">
         <v>3</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="61">
         <v>37</v>
       </c>
       <c r="D9" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="75" t="s">
         <v>87</v>
-      </c>
-      <c r="E9" s="75" t="s">
-        <v>88</v>
       </c>
       <c r="F9" s="69">
         <v>2.0199999999999999E-2</v>
@@ -3677,7 +3687,7 @@
       </c>
       <c r="M9" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N9" s="127">
         <f t="shared" si="5"/>
@@ -3689,11 +3699,11 @@
       </c>
       <c r="P9" s="73">
         <f t="shared" si="7"/>
-        <v>116853.37</v>
+        <v>135155.37</v>
       </c>
       <c r="Q9" s="74">
         <f t="shared" si="8"/>
-        <v>120359.37</v>
+        <v>139210.37</v>
       </c>
       <c r="R9" s="44">
         <f t="shared" si="9"/>
@@ -3701,21 +3711,21 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61">
         <v>4</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="61">
         <v>38</v>
       </c>
       <c r="D10" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="186" t="s">
         <v>90</v>
-      </c>
-      <c r="E10" s="187" t="s">
-        <v>91</v>
       </c>
       <c r="F10" s="69">
         <v>1.3899999999999999E-2</v>
@@ -3745,7 +3755,7 @@
       </c>
       <c r="M10" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N10" s="127">
         <f t="shared" si="5"/>
@@ -3757,29 +3767,29 @@
       </c>
       <c r="P10" s="73">
         <f t="shared" si="7"/>
-        <v>166932.38</v>
+        <v>179526.38</v>
       </c>
       <c r="Q10" s="74">
         <f t="shared" si="8"/>
-        <v>171940.38</v>
+        <v>184912.38</v>
       </c>
       <c r="R10" s="44">
         <f t="shared" si="9"/>
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61">
         <v>5</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="61">
         <v>39</v>
       </c>
       <c r="D11" s="60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="60"/>
       <c r="F11" s="69">
@@ -3810,7 +3820,7 @@
       </c>
       <c r="M11" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N11" s="127">
         <f t="shared" si="5"/>
@@ -3822,29 +3832,29 @@
       </c>
       <c r="P11" s="73">
         <f t="shared" si="7"/>
-        <v>100253.39</v>
+        <v>112847.39</v>
       </c>
       <c r="Q11" s="74">
         <f t="shared" si="8"/>
-        <v>103261.39</v>
+        <v>116232.39</v>
       </c>
       <c r="R11" s="44">
         <f t="shared" si="9"/>
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="61">
         <v>6</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="61">
         <v>40</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="75"/>
       <c r="F12" s="69">
@@ -3875,7 +3885,7 @@
       </c>
       <c r="M12" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N12" s="127">
         <f t="shared" si="5"/>
@@ -3887,32 +3897,32 @@
       </c>
       <c r="P12" s="73">
         <f t="shared" si="7"/>
-        <v>145693.4</v>
+        <v>163995.4</v>
       </c>
       <c r="Q12" s="74">
         <f t="shared" si="8"/>
-        <v>150064.4</v>
+        <v>168915.4</v>
       </c>
       <c r="R12" s="44">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61">
         <v>7</v>
       </c>
       <c r="B13" s="61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="61">
         <v>41</v>
       </c>
       <c r="D13" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="75" t="s">
         <v>97</v>
-      </c>
-      <c r="E13" s="75" t="s">
-        <v>98</v>
       </c>
       <c r="F13" s="69">
         <v>2.0199999999999999E-2</v>
@@ -3942,7 +3952,7 @@
       </c>
       <c r="M13" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N13" s="127">
         <f t="shared" si="5"/>
@@ -3954,32 +3964,32 @@
       </c>
       <c r="P13" s="73">
         <f t="shared" si="7"/>
-        <v>192089.41</v>
+        <v>210392.41</v>
       </c>
       <c r="Q13" s="74">
         <f t="shared" si="8"/>
-        <v>197852.41</v>
+        <v>216704.41</v>
       </c>
       <c r="R13" s="44">
         <f t="shared" si="9"/>
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="61">
         <v>8</v>
       </c>
       <c r="B14" s="61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="61">
         <v>42</v>
       </c>
       <c r="D14" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="60" t="s">
         <v>100</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>101</v>
       </c>
       <c r="F14" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4009,7 +4019,7 @@
       </c>
       <c r="M14" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N14" s="127">
         <f t="shared" si="5"/>
@@ -4021,32 +4031,32 @@
       </c>
       <c r="P14" s="73">
         <f t="shared" si="7"/>
-        <v>100253.42</v>
+        <v>112847.42</v>
       </c>
       <c r="Q14" s="74">
         <f t="shared" si="8"/>
-        <v>103261.42</v>
+        <v>116232.42</v>
       </c>
       <c r="R14" s="44">
         <f t="shared" si="9"/>
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="61">
         <v>1</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="61">
         <v>43</v>
       </c>
       <c r="D15" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4076,7 +4086,7 @@
       </c>
       <c r="M15" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N15" s="127">
         <f t="shared" si="5"/>
@@ -4088,32 +4098,32 @@
       </c>
       <c r="P15" s="73">
         <f t="shared" si="7"/>
-        <v>100253.43</v>
+        <v>112847.43</v>
       </c>
       <c r="Q15" s="74">
         <f t="shared" si="8"/>
-        <v>103261.43</v>
+        <v>116232.43</v>
       </c>
       <c r="R15" s="44">
         <f t="shared" si="9"/>
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="61">
         <v>1</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="61">
         <v>44</v>
       </c>
       <c r="D16" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="75" t="s">
         <v>105</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>106</v>
       </c>
       <c r="F16" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4143,7 +4153,7 @@
       </c>
       <c r="M16" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N16" s="127">
         <f t="shared" si="5"/>
@@ -4155,32 +4165,32 @@
       </c>
       <c r="P16" s="73">
         <f t="shared" si="7"/>
-        <v>145692.44</v>
+        <v>163994.44</v>
       </c>
       <c r="Q16" s="74">
         <f t="shared" si="8"/>
-        <v>150063.44</v>
+        <v>168914.44</v>
       </c>
       <c r="R16" s="44">
         <f t="shared" si="9"/>
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="61">
         <v>2</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="61">
         <v>45</v>
       </c>
       <c r="D17" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F17" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4210,7 +4220,7 @@
       </c>
       <c r="M17" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N17" s="127">
         <f t="shared" si="5"/>
@@ -4222,32 +4232,32 @@
       </c>
       <c r="P17" s="73">
         <f t="shared" si="7"/>
-        <v>145692.45000000001</v>
+        <v>163994.45000000001</v>
       </c>
       <c r="Q17" s="74">
         <f t="shared" si="8"/>
-        <v>150063.45000000001</v>
+        <v>168914.45</v>
       </c>
       <c r="R17" s="44">
         <f t="shared" si="9"/>
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="61">
         <v>2</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="61">
         <v>46</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4277,7 +4287,7 @@
       </c>
       <c r="M18" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N18" s="127">
         <f t="shared" si="5"/>
@@ -4289,11 +4299,11 @@
       </c>
       <c r="P18" s="73">
         <f t="shared" si="7"/>
-        <v>100253.46</v>
+        <v>112847.46</v>
       </c>
       <c r="Q18" s="74">
         <f t="shared" si="8"/>
-        <v>103261.46</v>
+        <v>116232.46</v>
       </c>
       <c r="R18" s="44">
         <f t="shared" si="9"/>
@@ -4301,21 +4311,21 @@
       </c>
       <c r="S18" s="120"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61">
         <v>3</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" s="61">
         <v>47</v>
       </c>
       <c r="D19" s="142" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" s="175" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F19" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4345,7 +4355,7 @@
       </c>
       <c r="M19" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N19" s="127">
         <f t="shared" si="5"/>
@@ -4357,11 +4367,11 @@
       </c>
       <c r="P19" s="73">
         <f t="shared" si="7"/>
-        <v>92464.47</v>
+        <v>105058.47</v>
       </c>
       <c r="Q19" s="74">
         <f t="shared" si="8"/>
-        <v>95238.47</v>
+        <v>108210.47</v>
       </c>
       <c r="R19" s="44">
         <f t="shared" si="9"/>
@@ -4369,21 +4379,21 @@
       </c>
       <c r="S19" s="120"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="61">
         <v>3</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="61">
         <v>48</v>
       </c>
       <c r="D20" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="60" t="s">
         <v>114</v>
-      </c>
-      <c r="E20" s="60" t="s">
-        <v>115</v>
       </c>
       <c r="F20" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4413,7 +4423,7 @@
       </c>
       <c r="M20" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N20" s="127">
         <f t="shared" si="5"/>
@@ -4425,11 +4435,11 @@
       </c>
       <c r="P20" s="73">
         <f t="shared" si="7"/>
-        <v>145692.48000000001</v>
+        <v>163994.48000000001</v>
       </c>
       <c r="Q20" s="74">
         <f t="shared" si="8"/>
-        <v>150063.48000000001</v>
+        <v>168914.48</v>
       </c>
       <c r="R20" s="44">
         <f t="shared" si="9"/>
@@ -4438,21 +4448,21 @@
       <c r="S20" s="120"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="61">
         <v>4</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" s="61">
         <v>49</v>
       </c>
       <c r="D21" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F21" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4482,7 +4492,7 @@
       </c>
       <c r="M21" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N21" s="127">
         <f t="shared" si="5"/>
@@ -4494,29 +4504,29 @@
       </c>
       <c r="P21" s="73">
         <f t="shared" si="7"/>
-        <v>145692.49</v>
+        <v>163994.49</v>
       </c>
       <c r="Q21" s="74">
         <f t="shared" si="8"/>
-        <v>150063.49</v>
+        <v>168914.49</v>
       </c>
       <c r="R21" s="44">
         <f t="shared" si="9"/>
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="61">
         <v>4</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22" s="61">
         <v>50</v>
       </c>
       <c r="D22" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="178"/>
       <c r="F22" s="69">
@@ -4544,7 +4554,7 @@
       </c>
       <c r="M22" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N22" s="127">
         <f t="shared" si="5"/>
@@ -4556,32 +4566,32 @@
       </c>
       <c r="P22" s="73">
         <f t="shared" si="7"/>
-        <v>574079.5</v>
+        <v>586673.5</v>
       </c>
       <c r="Q22" s="74">
         <f t="shared" si="8"/>
-        <v>591301.5</v>
+        <v>604273.5</v>
       </c>
       <c r="R22" s="44">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="61">
         <v>5</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C23" s="61">
         <v>51</v>
       </c>
       <c r="D23" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" s="75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F23" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4608,7 +4618,7 @@
       </c>
       <c r="M23" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N23" s="127">
         <f t="shared" si="5"/>
@@ -4620,32 +4630,32 @@
       </c>
       <c r="P23" s="73">
         <f t="shared" si="7"/>
-        <v>394277.51</v>
+        <v>406871.51</v>
       </c>
       <c r="Q23" s="74">
         <f t="shared" si="8"/>
-        <v>406105.51</v>
+        <v>419077.51</v>
       </c>
       <c r="R23" s="44">
         <f t="shared" si="9"/>
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="61">
         <v>5</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" s="61">
         <v>52</v>
       </c>
       <c r="D24" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="60" t="s">
         <v>122</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>123</v>
       </c>
       <c r="F24" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4675,7 +4685,7 @@
       </c>
       <c r="M24" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N24" s="127">
         <f t="shared" si="5"/>
@@ -4687,29 +4697,29 @@
       </c>
       <c r="P24" s="73">
         <f t="shared" si="7"/>
-        <v>145692.51999999999</v>
+        <v>163994.51999999999</v>
       </c>
       <c r="Q24" s="74">
         <f t="shared" si="8"/>
-        <v>150063.51999999999</v>
+        <v>168914.52</v>
       </c>
       <c r="R24" s="44">
         <f t="shared" si="9"/>
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="61">
         <v>6</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="61">
         <v>53</v>
       </c>
       <c r="D25" s="60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" s="75"/>
       <c r="F25" s="69">
@@ -4740,7 +4750,7 @@
       </c>
       <c r="M25" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N25" s="127">
         <f t="shared" si="5"/>
@@ -4752,32 +4762,32 @@
       </c>
       <c r="P25" s="73">
         <f t="shared" si="7"/>
-        <v>141065.53</v>
+        <v>159367.53</v>
       </c>
       <c r="Q25" s="74">
         <f t="shared" si="8"/>
-        <v>145297.53</v>
+        <v>164148.53</v>
       </c>
       <c r="R25" s="44">
         <f t="shared" si="9"/>
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="61">
         <v>6</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C26" s="61">
         <v>54</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" s="75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4807,7 +4817,7 @@
       </c>
       <c r="M26" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N26" s="127">
         <f t="shared" si="5"/>
@@ -4819,32 +4829,32 @@
       </c>
       <c r="P26" s="73">
         <f t="shared" si="7"/>
-        <v>97010.54</v>
+        <v>109604.54</v>
       </c>
       <c r="Q26" s="74">
         <f t="shared" si="8"/>
-        <v>99920.54</v>
+        <v>112892.54</v>
       </c>
       <c r="R26" s="44">
         <f t="shared" si="9"/>
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="61">
         <v>7</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C27" s="61">
         <v>55</v>
       </c>
       <c r="D27" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="75" t="s">
         <v>129</v>
-      </c>
-      <c r="E27" s="75" t="s">
-        <v>130</v>
       </c>
       <c r="F27" s="69">
         <v>1.3899999999999999E-2</v>
@@ -4874,7 +4884,7 @@
       </c>
       <c r="M27" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N27" s="127">
         <f t="shared" si="5"/>
@@ -4886,32 +4896,32 @@
       </c>
       <c r="P27" s="73">
         <f t="shared" si="7"/>
-        <v>117734.55</v>
+        <v>130328.55</v>
       </c>
       <c r="Q27" s="74">
         <f t="shared" si="8"/>
-        <v>121266.55</v>
+        <v>134238.54999999999</v>
       </c>
       <c r="R27" s="44">
         <f t="shared" si="9"/>
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="61">
         <v>7</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28" s="61">
         <v>56</v>
       </c>
       <c r="D28" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="75" t="s">
         <v>132</v>
-      </c>
-      <c r="E28" s="75" t="s">
-        <v>133</v>
       </c>
       <c r="F28" s="69">
         <v>2.0199999999999999E-2</v>
@@ -4941,7 +4951,7 @@
       </c>
       <c r="M28" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N28" s="127">
         <f t="shared" si="5"/>
@@ -4953,29 +4963,29 @@
       </c>
       <c r="P28" s="73">
         <f t="shared" si="7"/>
-        <v>145670.56</v>
+        <v>163972.56</v>
       </c>
       <c r="Q28" s="74">
         <f t="shared" si="8"/>
-        <v>150040.56</v>
+        <v>168891.56</v>
       </c>
       <c r="R28" s="44">
         <f t="shared" si="9"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="61">
         <v>8</v>
       </c>
       <c r="B29" s="61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C29" s="61">
         <v>57</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E29" s="60"/>
       <c r="F29" s="69">
@@ -5006,7 +5016,7 @@
       </c>
       <c r="M29" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N29" s="127">
         <f t="shared" si="5"/>
@@ -5018,32 +5028,32 @@
       </c>
       <c r="P29" s="73">
         <f t="shared" si="7"/>
-        <v>145692.57</v>
+        <v>163994.57</v>
       </c>
       <c r="Q29" s="74">
         <f t="shared" si="8"/>
-        <v>150063.57</v>
+        <v>168914.57</v>
       </c>
       <c r="R29" s="44">
         <f t="shared" si="9"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="61">
         <v>8</v>
       </c>
       <c r="B30" s="61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C30" s="61">
         <v>58</v>
       </c>
       <c r="D30" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="60" t="s">
         <v>137</v>
-      </c>
-      <c r="E30" s="60" t="s">
-        <v>138</v>
       </c>
       <c r="F30" s="69">
         <v>1.3899999999999999E-2</v>
@@ -5073,7 +5083,7 @@
       </c>
       <c r="M30" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N30" s="127">
         <f t="shared" si="5"/>
@@ -5085,29 +5095,29 @@
       </c>
       <c r="P30" s="73">
         <f t="shared" si="7"/>
-        <v>83572.58</v>
+        <v>96166.58</v>
       </c>
       <c r="Q30" s="74">
         <f t="shared" si="8"/>
-        <v>86079.58</v>
+        <v>99051.58</v>
       </c>
       <c r="R30" s="44">
         <f t="shared" si="9"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="61">
         <v>9</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="61">
         <v>59</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E31" s="75"/>
       <c r="F31" s="69">
@@ -5135,7 +5145,7 @@
       </c>
       <c r="M31" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N31" s="127">
         <f t="shared" si="5"/>
@@ -5147,32 +5157,32 @@
       </c>
       <c r="P31" s="73">
         <f t="shared" si="7"/>
-        <v>211586.59</v>
+        <v>224180.59</v>
       </c>
       <c r="Q31" s="74">
         <f t="shared" si="8"/>
-        <v>217934.59</v>
+        <v>230905.59</v>
       </c>
       <c r="R31" s="44">
         <f t="shared" si="9"/>
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="61">
         <v>9</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C32" s="61">
         <v>60</v>
       </c>
       <c r="D32" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="60" t="s">
         <v>142</v>
-      </c>
-      <c r="E32" s="60" t="s">
-        <v>143</v>
       </c>
       <c r="F32" s="69">
         <v>2.0199999999999999E-2</v>
@@ -5202,7 +5212,7 @@
       </c>
       <c r="M32" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N32" s="127">
         <f t="shared" si="5"/>
@@ -5214,29 +5224,29 @@
       </c>
       <c r="P32" s="73">
         <f t="shared" si="7"/>
-        <v>145692.6</v>
+        <v>163994.6</v>
       </c>
       <c r="Q32" s="74">
         <f t="shared" si="8"/>
-        <v>150063.6</v>
+        <v>168914.6</v>
       </c>
       <c r="R32" s="44">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="61">
         <v>10</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C33" s="61">
         <v>61</v>
       </c>
       <c r="D33" s="60" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E33" s="60"/>
       <c r="F33" s="69">
@@ -5267,7 +5277,7 @@
       </c>
       <c r="M33" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N33" s="127">
         <f t="shared" si="5"/>
@@ -5279,32 +5289,32 @@
       </c>
       <c r="P33" s="73">
         <f t="shared" si="7"/>
-        <v>145692.60999999999</v>
+        <v>163994.60999999999</v>
       </c>
       <c r="Q33" s="74">
         <f t="shared" si="8"/>
-        <v>150063.60999999999</v>
+        <v>168914.61</v>
       </c>
       <c r="R33" s="44">
         <f t="shared" si="9"/>
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="61">
         <v>10</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C34" s="61">
         <v>62</v>
       </c>
       <c r="D34" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="60" t="s">
         <v>147</v>
-      </c>
-      <c r="E34" s="60" t="s">
-        <v>148</v>
       </c>
       <c r="F34" s="69">
         <v>1.3899999999999999E-2</v>
@@ -5334,7 +5344,7 @@
       </c>
       <c r="M34" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N34" s="127">
         <f t="shared" si="5"/>
@@ -5346,32 +5356,32 @@
       </c>
       <c r="P34" s="73">
         <f t="shared" si="7"/>
-        <v>100253.62</v>
+        <v>112847.62</v>
       </c>
       <c r="Q34" s="74">
         <f t="shared" si="8"/>
-        <v>103261.62</v>
+        <v>116232.62</v>
       </c>
       <c r="R34" s="44">
         <f t="shared" si="9"/>
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="61">
         <v>11</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="61">
         <v>63</v>
       </c>
       <c r="D35" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="60" t="s">
         <v>150</v>
-      </c>
-      <c r="E35" s="60" t="s">
-        <v>151</v>
       </c>
       <c r="F35" s="69">
         <v>1.3899999999999999E-2</v>
@@ -5401,7 +5411,7 @@
       </c>
       <c r="M35" s="127">
         <f t="shared" si="4"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N35" s="127">
         <f t="shared" si="5"/>
@@ -5413,32 +5423,32 @@
       </c>
       <c r="P35" s="73">
         <f t="shared" si="7"/>
-        <v>100253.63</v>
+        <v>112847.63</v>
       </c>
       <c r="Q35" s="74">
         <f t="shared" si="8"/>
-        <v>103261.63</v>
+        <v>116232.63</v>
       </c>
       <c r="R35" s="44">
         <f t="shared" si="9"/>
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="61">
         <v>11</v>
       </c>
       <c r="B36" s="61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="61">
         <v>64</v>
       </c>
       <c r="D36" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="75" t="s">
         <v>153</v>
-      </c>
-      <c r="E36" s="75" t="s">
-        <v>154</v>
       </c>
       <c r="F36" s="69">
         <v>2.0199999999999999E-2</v>
@@ -5468,7 +5478,7 @@
       </c>
       <c r="M36" s="127">
         <f t="shared" si="4"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N36" s="127">
         <f t="shared" si="5"/>
@@ -5480,32 +5490,32 @@
       </c>
       <c r="P36" s="73">
         <f t="shared" si="7"/>
-        <v>169987.64</v>
+        <v>188290.64</v>
       </c>
       <c r="Q36" s="74">
         <f t="shared" si="8"/>
-        <v>175087.64</v>
+        <v>193939.64</v>
       </c>
       <c r="R36" s="44">
         <f t="shared" si="9"/>
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="61">
         <v>12</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="61">
         <v>65</v>
       </c>
       <c r="D37" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="75" t="s">
         <v>156</v>
-      </c>
-      <c r="E37" s="75" t="s">
-        <v>157</v>
       </c>
       <c r="F37" s="69">
         <v>2.0199999999999999E-2</v>
@@ -5535,7 +5545,7 @@
       </c>
       <c r="M37" s="127">
         <f t="shared" ref="M37:M56" si="14">F$1*F37</f>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N37" s="127">
         <f t="shared" ref="N37:N56" si="15">F$2*F37</f>
@@ -5547,32 +5557,32 @@
       </c>
       <c r="P37" s="73">
         <f t="shared" ref="P37:P68" si="17">ROUND(SUM(I37:O37),0) + R37</f>
-        <v>145692.65</v>
+        <v>163994.65</v>
       </c>
       <c r="Q37" s="74">
         <f t="shared" ref="Q37:Q56" si="18">ROUND(P37*3%,0) + P37</f>
-        <v>150063.65</v>
+        <v>168914.65</v>
       </c>
       <c r="R37" s="44">
         <f t="shared" ref="R37:R68" si="19">ROUND(0.001+C37/100,2)</f>
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="61">
         <v>12</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C38" s="61">
         <v>66</v>
       </c>
       <c r="D38" s="142" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="142" t="s">
         <v>159</v>
-      </c>
-      <c r="E38" s="142" t="s">
-        <v>160</v>
       </c>
       <c r="F38" s="69">
         <v>1.3899999999999999E-2</v>
@@ -5602,7 +5612,7 @@
       </c>
       <c r="M38" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N38" s="127">
         <f t="shared" si="15"/>
@@ -5614,32 +5624,32 @@
       </c>
       <c r="P38" s="73">
         <f t="shared" si="17"/>
-        <v>211585.66</v>
+        <v>224179.66</v>
       </c>
       <c r="Q38" s="74">
         <f t="shared" si="18"/>
-        <v>217933.66</v>
+        <v>230904.66</v>
       </c>
       <c r="R38" s="44">
         <f t="shared" si="19"/>
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="61">
         <v>1</v>
       </c>
       <c r="B39" s="61" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C39" s="61">
         <v>67</v>
       </c>
       <c r="D39" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="75" t="s">
         <v>162</v>
-      </c>
-      <c r="E39" s="75" t="s">
-        <v>163</v>
       </c>
       <c r="F39" s="69">
         <v>1.3899999999999999E-2</v>
@@ -5669,7 +5679,7 @@
       </c>
       <c r="M39" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N39" s="127">
         <f t="shared" si="15"/>
@@ -5681,29 +5691,29 @@
       </c>
       <c r="P39" s="73">
         <f t="shared" si="17"/>
-        <v>117433.67</v>
+        <v>130027.67</v>
       </c>
       <c r="Q39" s="74">
         <f t="shared" si="18"/>
-        <v>120956.67</v>
+        <v>133928.66999999998</v>
       </c>
       <c r="R39" s="44">
         <f t="shared" si="19"/>
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="61">
         <v>1</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="61">
         <v>68</v>
       </c>
       <c r="D40" s="60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="75" t="str">
         <f>D76</f>
@@ -5737,7 +5747,7 @@
       </c>
       <c r="M40" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N40" s="127">
         <f t="shared" si="15"/>
@@ -5749,32 +5759,32 @@
       </c>
       <c r="P40" s="73">
         <f t="shared" si="17"/>
-        <v>145692.68</v>
+        <v>163994.68</v>
       </c>
       <c r="Q40" s="74">
         <f t="shared" si="18"/>
-        <v>150063.67999999999</v>
+        <v>168914.68</v>
       </c>
       <c r="R40" s="44">
         <f t="shared" si="19"/>
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="60">
         <v>1</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41" s="61">
         <v>69</v>
       </c>
       <c r="D41" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="75" t="s">
         <v>167</v>
-      </c>
-      <c r="E41" s="75" t="s">
-        <v>168</v>
       </c>
       <c r="F41" s="76">
         <v>2.0199999999999999E-2</v>
@@ -5803,7 +5813,7 @@
       </c>
       <c r="M41" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N41" s="127">
         <f t="shared" si="15"/>
@@ -5815,32 +5825,32 @@
       </c>
       <c r="P41" s="73">
         <f t="shared" si="17"/>
-        <v>145677.69</v>
+        <v>163979.69</v>
       </c>
       <c r="Q41" s="74">
         <f t="shared" si="18"/>
-        <v>150047.69</v>
+        <v>168898.69</v>
       </c>
       <c r="R41" s="44">
         <f t="shared" si="19"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="61">
         <v>2</v>
       </c>
       <c r="B42" s="77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" s="61">
         <v>70</v>
       </c>
       <c r="D42" s="60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" s="60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F42" s="76">
         <v>1.3899999999999999E-2</v>
@@ -5870,7 +5880,7 @@
       </c>
       <c r="M42" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N42" s="127">
         <f t="shared" si="15"/>
@@ -5882,32 +5892,32 @@
       </c>
       <c r="P42" s="73">
         <f t="shared" si="17"/>
-        <v>248195.7</v>
+        <v>260789.7</v>
       </c>
       <c r="Q42" s="74">
         <f t="shared" si="18"/>
-        <v>255641.7</v>
+        <v>268613.7</v>
       </c>
       <c r="R42" s="44">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="61">
         <v>2</v>
       </c>
       <c r="B43" s="77" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="61">
         <v>71</v>
       </c>
       <c r="D43" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" s="75" t="s">
         <v>172</v>
-      </c>
-      <c r="E43" s="75" t="s">
-        <v>173</v>
       </c>
       <c r="F43" s="76">
         <v>1.3899999999999999E-2</v>
@@ -5937,7 +5947,7 @@
       </c>
       <c r="M43" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N43" s="127">
         <f t="shared" si="15"/>
@@ -5949,32 +5959,32 @@
       </c>
       <c r="P43" s="73">
         <f t="shared" si="17"/>
-        <v>100254.71</v>
+        <v>112848.71</v>
       </c>
       <c r="Q43" s="74">
         <f t="shared" si="18"/>
-        <v>103262.71</v>
+        <v>116233.71</v>
       </c>
       <c r="R43" s="44">
         <f t="shared" si="19"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="61">
         <v>2</v>
       </c>
       <c r="B44" s="77" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C44" s="61">
         <v>72</v>
       </c>
       <c r="D44" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E44" s="60" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F44" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6001,7 +6011,7 @@
       </c>
       <c r="M44" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N44" s="127">
         <f t="shared" si="15"/>
@@ -6013,32 +6023,32 @@
       </c>
       <c r="P44" s="73">
         <f t="shared" si="17"/>
-        <v>465918.71999999997</v>
+        <v>484220.72</v>
       </c>
       <c r="Q44" s="74">
         <f t="shared" si="18"/>
-        <v>479896.72</v>
+        <v>498747.72</v>
       </c>
       <c r="R44" s="44">
         <f t="shared" si="19"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="61">
         <v>3</v>
       </c>
       <c r="B45" s="77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C45" s="61">
         <v>73</v>
       </c>
       <c r="D45" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="E45" s="60" t="s">
         <v>176</v>
-      </c>
-      <c r="E45" s="60" t="s">
-        <v>177</v>
       </c>
       <c r="F45" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6065,7 +6075,7 @@
       </c>
       <c r="M45" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N45" s="127">
         <f t="shared" si="15"/>
@@ -6077,32 +6087,32 @@
       </c>
       <c r="P45" s="73">
         <f t="shared" si="17"/>
-        <v>471172.73</v>
+        <v>489474.73</v>
       </c>
       <c r="Q45" s="74">
         <f t="shared" si="18"/>
-        <v>485307.73</v>
+        <v>504158.73</v>
       </c>
       <c r="R45" s="44">
         <f t="shared" si="19"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="61">
         <v>3</v>
       </c>
       <c r="B46" s="77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C46" s="61">
         <v>74</v>
       </c>
       <c r="D46" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" s="75" t="s">
         <v>179</v>
-      </c>
-      <c r="E46" s="75" t="s">
-        <v>180</v>
       </c>
       <c r="F46" s="76">
         <v>1.3899999999999999E-2</v>
@@ -6132,7 +6142,7 @@
       </c>
       <c r="M46" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N46" s="127">
         <f t="shared" si="15"/>
@@ -6144,32 +6154,32 @@
       </c>
       <c r="P46" s="73">
         <f t="shared" si="17"/>
-        <v>100253.74</v>
+        <v>112847.74</v>
       </c>
       <c r="Q46" s="74">
         <f t="shared" si="18"/>
-        <v>103261.74</v>
+        <v>116232.74</v>
       </c>
       <c r="R46" s="44">
         <f t="shared" si="19"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="61">
         <v>3</v>
       </c>
       <c r="B47" s="77" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C47" s="61">
         <v>75</v>
       </c>
       <c r="D47" s="60" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47" s="75" t="s">
         <v>182</v>
-      </c>
-      <c r="E47" s="75" t="s">
-        <v>183</v>
       </c>
       <c r="F47" s="76">
         <v>1.3899999999999999E-2</v>
@@ -6199,7 +6209,7 @@
       </c>
       <c r="M47" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N47" s="127">
         <f t="shared" si="15"/>
@@ -6211,11 +6221,11 @@
       </c>
       <c r="P47" s="73">
         <f t="shared" si="17"/>
-        <v>100253.75</v>
+        <v>112847.75</v>
       </c>
       <c r="Q47" s="74">
         <f t="shared" si="18"/>
-        <v>103261.75</v>
+        <v>116232.75</v>
       </c>
       <c r="R47" s="44">
         <f t="shared" si="19"/>
@@ -6223,21 +6233,21 @@
       </c>
       <c r="T47" s="146"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="61">
         <v>4</v>
       </c>
       <c r="B48" s="77" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C48" s="61">
         <v>76</v>
       </c>
       <c r="D48" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" s="129" t="s">
         <v>185</v>
-      </c>
-      <c r="E48" s="129" t="s">
-        <v>186</v>
       </c>
       <c r="F48" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6267,7 +6277,7 @@
       </c>
       <c r="M48" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N48" s="127">
         <f t="shared" si="15"/>
@@ -6279,32 +6289,32 @@
       </c>
       <c r="P48" s="73">
         <f t="shared" si="17"/>
-        <v>145692.76</v>
+        <v>163994.76</v>
       </c>
       <c r="Q48" s="74">
         <f t="shared" si="18"/>
-        <v>150063.76</v>
+        <v>168914.76</v>
       </c>
       <c r="R48" s="44">
         <f t="shared" si="19"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="61">
         <v>4</v>
       </c>
       <c r="B49" s="77" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C49" s="61">
         <v>77</v>
       </c>
       <c r="D49" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E49" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F49" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6334,7 +6344,7 @@
       </c>
       <c r="M49" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N49" s="127">
         <f t="shared" si="15"/>
@@ -6346,32 +6356,32 @@
       </c>
       <c r="P49" s="73">
         <f t="shared" si="17"/>
-        <v>145692.76999999999</v>
+        <v>163994.76999999999</v>
       </c>
       <c r="Q49" s="74">
         <f t="shared" si="18"/>
-        <v>150063.76999999999</v>
+        <v>168914.77</v>
       </c>
       <c r="R49" s="44">
         <f t="shared" si="19"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="61">
         <v>4</v>
       </c>
       <c r="B50" s="77" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C50" s="61">
         <v>78</v>
       </c>
       <c r="D50" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E50" s="60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F50" s="76">
         <v>1.3899999999999999E-2</v>
@@ -6398,7 +6408,7 @@
       </c>
       <c r="M50" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N50" s="127">
         <f t="shared" si="15"/>
@@ -6410,29 +6420,29 @@
       </c>
       <c r="P50" s="73">
         <f t="shared" si="17"/>
-        <v>427555.78</v>
+        <v>440149.78</v>
       </c>
       <c r="Q50" s="74">
         <f t="shared" si="18"/>
-        <v>440382.78</v>
+        <v>453353.78</v>
       </c>
       <c r="R50" s="44">
         <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="61">
         <v>5</v>
       </c>
       <c r="B51" s="77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C51" s="61">
         <v>79</v>
       </c>
       <c r="D51" s="60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E51" s="75"/>
       <c r="F51" s="76">
@@ -6463,7 +6473,7 @@
       </c>
       <c r="M51" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N51" s="127">
         <f t="shared" si="15"/>
@@ -6475,32 +6485,32 @@
       </c>
       <c r="P51" s="73">
         <f t="shared" si="17"/>
-        <v>100253.79</v>
+        <v>112847.79</v>
       </c>
       <c r="Q51" s="74">
         <f t="shared" si="18"/>
-        <v>103261.79</v>
+        <v>116232.79</v>
       </c>
       <c r="R51" s="44">
         <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="61">
         <v>5</v>
       </c>
       <c r="B52" s="77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C52" s="61">
         <v>80</v>
       </c>
       <c r="D52" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="E52" s="60" t="s">
         <v>194</v>
-      </c>
-      <c r="E52" s="60" t="s">
-        <v>195</v>
       </c>
       <c r="F52" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6530,7 +6540,7 @@
       </c>
       <c r="M52" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N52" s="127">
         <f t="shared" si="15"/>
@@ -6542,32 +6552,32 @@
       </c>
       <c r="P52" s="73">
         <f t="shared" si="17"/>
-        <v>277978.8</v>
+        <v>296280.8</v>
       </c>
       <c r="Q52" s="74">
         <f t="shared" si="18"/>
-        <v>286317.8</v>
+        <v>305168.8</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="61">
         <v>5</v>
       </c>
       <c r="B53" s="77" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C53" s="61">
         <v>81</v>
       </c>
       <c r="D53" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="E53" s="60" t="s">
         <v>197</v>
-      </c>
-      <c r="E53" s="60" t="s">
-        <v>198</v>
       </c>
       <c r="F53" s="76">
         <v>2.0199999999999999E-2</v>
@@ -6597,7 +6607,7 @@
       </c>
       <c r="M53" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N53" s="127">
         <f t="shared" si="15"/>
@@ -6609,32 +6619,32 @@
       </c>
       <c r="P53" s="73">
         <f t="shared" si="17"/>
-        <v>145692.81</v>
+        <v>163994.81</v>
       </c>
       <c r="Q53" s="74">
         <f t="shared" si="18"/>
-        <v>150063.81</v>
+        <v>168914.81</v>
       </c>
       <c r="R53" s="44">
         <f t="shared" si="19"/>
         <v>0.81</v>
       </c>
       <c r="T53" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="61">
         <v>6</v>
       </c>
       <c r="B54" s="77" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C54" s="61">
         <v>82</v>
       </c>
       <c r="D54" s="60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E54" s="60"/>
       <c r="F54" s="76">
@@ -6665,7 +6675,7 @@
       </c>
       <c r="M54" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N54" s="127">
         <f t="shared" si="15"/>
@@ -6677,32 +6687,32 @@
       </c>
       <c r="P54" s="73">
         <f t="shared" si="17"/>
-        <v>100253.82</v>
+        <v>112847.82</v>
       </c>
       <c r="Q54" s="74">
         <f t="shared" si="18"/>
-        <v>103261.82</v>
+        <v>116232.82</v>
       </c>
       <c r="R54" s="44">
         <f t="shared" si="19"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="61">
         <v>6</v>
       </c>
       <c r="B55" s="77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C55" s="61">
         <v>83</v>
       </c>
       <c r="D55" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="60" t="s">
         <v>202</v>
-      </c>
-      <c r="E55" s="60" t="s">
-        <v>203</v>
       </c>
       <c r="F55" s="76">
         <v>1.3899999999999999E-2</v>
@@ -6729,7 +6739,7 @@
       </c>
       <c r="M55" s="127">
         <f t="shared" si="14"/>
-        <v>17250.319223999999</v>
+        <v>29844.356399999997</v>
       </c>
       <c r="N55" s="127">
         <f t="shared" si="15"/>
@@ -6741,29 +6751,29 @@
       </c>
       <c r="P55" s="73">
         <f t="shared" si="17"/>
-        <v>324223.83</v>
+        <v>336817.83</v>
       </c>
       <c r="Q55" s="74">
         <f t="shared" si="18"/>
-        <v>333950.83</v>
+        <v>346922.83</v>
       </c>
       <c r="R55" s="44">
         <f t="shared" si="19"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="61">
         <v>6</v>
       </c>
       <c r="B56" s="77" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C56" s="61">
         <v>84</v>
       </c>
       <c r="D56" s="60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E56" s="75"/>
       <c r="F56" s="76">
@@ -6794,7 +6804,7 @@
       </c>
       <c r="M56" s="127">
         <f t="shared" si="14"/>
-        <v>25068.809231999996</v>
+        <v>43370.9352</v>
       </c>
       <c r="N56" s="127">
         <f t="shared" si="15"/>
@@ -6806,18 +6816,18 @@
       </c>
       <c r="P56" s="73">
         <f t="shared" si="17"/>
-        <v>145692.84</v>
+        <v>163994.84</v>
       </c>
       <c r="Q56" s="74">
         <f t="shared" si="18"/>
-        <v>150063.84</v>
+        <v>168914.84</v>
       </c>
       <c r="R56" s="44">
         <f t="shared" si="19"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="61">
         <v>7</v>
       </c>
@@ -6853,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="61">
         <v>7</v>
       </c>
@@ -6889,21 +6899,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="61">
         <v>7</v>
       </c>
       <c r="B59" s="77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C59" s="61">
         <v>17</v>
       </c>
       <c r="D59" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E59" s="60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="76">
         <v>3.2000000000000002E-3</v>
@@ -6933,7 +6943,7 @@
       </c>
       <c r="M59" s="127">
         <f t="shared" ref="M59:M90" si="23">F$1*F59</f>
-        <v>3971.2965119999999</v>
+        <v>6870.6432000000004</v>
       </c>
       <c r="N59" s="127">
         <f t="shared" ref="N59:N90" si="24">F$2*F59</f>
@@ -6945,29 +6955,29 @@
       </c>
       <c r="P59" s="73">
         <f t="shared" si="17"/>
-        <v>22286.17</v>
+        <v>25185.17</v>
       </c>
       <c r="Q59" s="74">
         <f t="shared" ref="Q59:Q90" si="25">ROUND(P59*3%,0) + P59</f>
-        <v>22955.17</v>
+        <v>25941.17</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="19"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="61">
         <v>8</v>
       </c>
       <c r="B60" s="77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C60" s="61">
         <v>18</v>
       </c>
       <c r="D60" s="60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E60" s="75"/>
       <c r="F60" s="76">
@@ -6995,7 +7005,7 @@
       </c>
       <c r="M60" s="127">
         <f t="shared" si="23"/>
-        <v>4095.3995279999999</v>
+        <v>7085.3508000000002</v>
       </c>
       <c r="N60" s="127">
         <f t="shared" si="24"/>
@@ -7007,29 +7017,29 @@
       </c>
       <c r="P60" s="73">
         <f t="shared" si="17"/>
-        <v>201811.18</v>
+        <v>204801.18</v>
       </c>
       <c r="Q60" s="74">
         <f t="shared" si="25"/>
-        <v>207865.18</v>
+        <v>210945.18</v>
       </c>
       <c r="R60" s="44">
         <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="61">
         <v>8</v>
       </c>
       <c r="B61" s="77" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C61" s="61">
         <v>19</v>
       </c>
       <c r="D61" s="60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E61" s="75"/>
       <c r="F61" s="76">
@@ -7057,7 +7067,7 @@
       </c>
       <c r="M61" s="127">
         <f t="shared" si="23"/>
-        <v>496.41206399999999</v>
+        <v>858.83040000000005</v>
       </c>
       <c r="N61" s="127">
         <f t="shared" si="24"/>
@@ -7069,29 +7079,29 @@
       </c>
       <c r="P61" s="73">
         <f t="shared" si="17"/>
-        <v>7081.19</v>
+        <v>7444.19</v>
       </c>
       <c r="Q61" s="74">
         <f t="shared" si="25"/>
-        <v>7293.19</v>
+        <v>7667.19</v>
       </c>
       <c r="R61" s="44">
         <f t="shared" si="19"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="61">
         <v>8</v>
       </c>
       <c r="B62" s="77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C62" s="61">
         <v>20</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
@@ -7121,7 +7131,7 @@
       </c>
       <c r="M62" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N62" s="127">
         <f t="shared" si="24"/>
@@ -7133,32 +7143,32 @@
       </c>
       <c r="P62" s="73">
         <f t="shared" si="17"/>
-        <v>1442.2</v>
+        <v>1624.2</v>
       </c>
       <c r="Q62" s="74">
         <f t="shared" si="25"/>
-        <v>1485.2</v>
+        <v>1673.2</v>
       </c>
       <c r="R62" s="44">
         <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="61">
         <v>9</v>
       </c>
       <c r="B63" s="77" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C63" s="61">
         <v>21</v>
       </c>
       <c r="D63" s="60" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E63" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F63" s="76">
         <v>2.0000000000000001E-4</v>
@@ -7188,7 +7198,7 @@
       </c>
       <c r="M63" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N63" s="127">
         <f t="shared" si="24"/>
@@ -7200,29 +7210,29 @@
       </c>
       <c r="P63" s="73">
         <f t="shared" si="17"/>
-        <v>-45074.79</v>
+        <v>-44893.79</v>
       </c>
       <c r="Q63" s="74">
         <f t="shared" si="25"/>
-        <v>-46426.79</v>
+        <v>-46240.79</v>
       </c>
       <c r="R63" s="44">
         <f t="shared" si="19"/>
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="61">
         <v>9</v>
       </c>
       <c r="B64" s="77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C64" s="61">
         <v>22</v>
       </c>
       <c r="D64" s="60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="75"/>
       <c r="F64" s="76">
@@ -7253,7 +7263,7 @@
       </c>
       <c r="M64" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N64" s="127">
         <f t="shared" si="24"/>
@@ -7265,32 +7275,32 @@
       </c>
       <c r="P64" s="73">
         <f t="shared" si="17"/>
-        <v>1442.22</v>
+        <v>1624.22</v>
       </c>
       <c r="Q64" s="74">
         <f t="shared" si="25"/>
-        <v>1485.22</v>
+        <v>1673.22</v>
       </c>
       <c r="R64" s="44">
         <f t="shared" si="19"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="61">
         <v>9</v>
       </c>
       <c r="B65" s="77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C65" s="61">
         <v>23</v>
       </c>
       <c r="D65" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E65" s="75" t="s">
         <v>132</v>
-      </c>
-      <c r="E65" s="75" t="s">
-        <v>133</v>
       </c>
       <c r="F65" s="76">
         <v>2.0000000000000001E-4</v>
@@ -7320,7 +7330,7 @@
       </c>
       <c r="M65" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N65" s="127">
         <f t="shared" si="24"/>
@@ -7332,29 +7342,29 @@
       </c>
       <c r="P65" s="73">
         <f t="shared" si="17"/>
-        <v>1202.23</v>
+        <v>1383.23</v>
       </c>
       <c r="Q65" s="74">
         <f t="shared" si="25"/>
-        <v>1238.23</v>
+        <v>1424.23</v>
       </c>
       <c r="R65" s="44">
         <f t="shared" si="19"/>
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="61">
         <v>10</v>
       </c>
       <c r="B66" s="77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C66" s="61">
         <v>24</v>
       </c>
       <c r="D66" s="60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E66" s="75"/>
       <c r="F66" s="76">
@@ -7385,7 +7395,7 @@
       </c>
       <c r="M66" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N66" s="127">
         <f t="shared" si="24"/>
@@ -7397,32 +7407,32 @@
       </c>
       <c r="P66" s="73">
         <f t="shared" si="17"/>
-        <v>1442.24</v>
+        <v>1624.24</v>
       </c>
       <c r="Q66" s="74">
         <f t="shared" si="25"/>
-        <v>1485.24</v>
+        <v>1673.24</v>
       </c>
       <c r="R66" s="44">
         <f t="shared" si="19"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="61">
         <v>10</v>
       </c>
       <c r="B67" s="77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C67" s="61">
         <v>25</v>
       </c>
       <c r="D67" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="E67" s="60" t="s">
         <v>219</v>
-      </c>
-      <c r="E67" s="60" t="s">
-        <v>220</v>
       </c>
       <c r="F67" s="76">
         <v>2.0000000000000001E-4</v>
@@ -7452,7 +7462,7 @@
       </c>
       <c r="M67" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N67" s="127">
         <f t="shared" si="24"/>
@@ -7464,31 +7474,31 @@
       </c>
       <c r="P67" s="73">
         <f t="shared" si="17"/>
-        <v>1442.25</v>
+        <v>1624.25</v>
       </c>
       <c r="Q67" s="74">
         <f t="shared" si="25"/>
-        <v>1485.25</v>
+        <v>1673.25</v>
       </c>
       <c r="R67" s="44">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="61">
         <v>10</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C68" s="61">
         <v>26</v>
       </c>
       <c r="D68" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="E68" s="224"/>
+        <v>136</v>
+      </c>
+      <c r="E68" s="188"/>
       <c r="F68" s="76">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -7517,7 +7527,7 @@
       </c>
       <c r="M68" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N68" s="127">
         <f t="shared" si="24"/>
@@ -7529,29 +7539,29 @@
       </c>
       <c r="P68" s="73">
         <f t="shared" si="17"/>
-        <v>1064.26</v>
+        <v>1245.26</v>
       </c>
       <c r="Q68" s="74">
         <f t="shared" si="25"/>
-        <v>1096.26</v>
+        <v>1282.26</v>
       </c>
       <c r="R68" s="44">
         <f t="shared" si="19"/>
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="61">
         <v>11</v>
       </c>
       <c r="B69" s="77" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C69" s="61">
         <v>27</v>
       </c>
       <c r="D69" s="60" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E69" s="75"/>
       <c r="F69" s="76">
@@ -7579,7 +7589,7 @@
       </c>
       <c r="M69" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N69" s="127">
         <f t="shared" si="24"/>
@@ -7591,29 +7601,29 @@
       </c>
       <c r="P69" s="73">
         <f t="shared" ref="P69:P90" si="28">ROUND(SUM(I69:O69),0) + R69</f>
-        <v>13721.27</v>
+        <v>13903.27</v>
       </c>
       <c r="Q69" s="74">
         <f t="shared" si="25"/>
-        <v>14133.27</v>
+        <v>14320.27</v>
       </c>
       <c r="R69" s="44">
         <f t="shared" ref="R69:R90" si="29">ROUND(0.001+C69/100,2)</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="61">
         <v>11</v>
       </c>
       <c r="B70" s="77" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C70" s="61">
         <v>28</v>
       </c>
       <c r="D70" s="60" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E70" s="75"/>
       <c r="F70" s="76">
@@ -7641,7 +7651,7 @@
       </c>
       <c r="M70" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N70" s="127">
         <f t="shared" si="24"/>
@@ -7653,32 +7663,32 @@
       </c>
       <c r="P70" s="73">
         <f t="shared" si="28"/>
-        <v>13721.28</v>
+        <v>13903.28</v>
       </c>
       <c r="Q70" s="74">
         <f t="shared" si="25"/>
-        <v>14133.28</v>
+        <v>14320.28</v>
       </c>
       <c r="R70" s="44">
         <f t="shared" si="29"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="61">
         <v>11</v>
       </c>
       <c r="B71" s="77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C71" s="61">
         <v>29</v>
       </c>
       <c r="D71" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E71" s="60" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F71" s="76">
         <v>2.0000000000000001E-4</v>
@@ -7705,7 +7715,7 @@
       </c>
       <c r="M71" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N71" s="127">
         <f t="shared" si="24"/>
@@ -7717,30 +7727,30 @@
       </c>
       <c r="P71" s="73">
         <f t="shared" si="28"/>
-        <v>2959.29</v>
+        <v>3140.29</v>
       </c>
       <c r="Q71" s="74">
         <f t="shared" si="25"/>
-        <v>3048.29</v>
+        <v>3234.29</v>
       </c>
       <c r="R71" s="44">
         <f t="shared" si="29"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="61"/>
       <c r="B72" s="78" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C72" s="61">
         <v>30</v>
       </c>
       <c r="D72" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E72" s="60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F72" s="80">
         <v>2.0000000000000001E-4</v>
@@ -7770,7 +7780,7 @@
       </c>
       <c r="M72" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N72" s="127">
         <f t="shared" si="24"/>
@@ -7782,27 +7792,27 @@
       </c>
       <c r="P72" s="73">
         <f t="shared" si="28"/>
-        <v>1442.3</v>
+        <v>1624.3</v>
       </c>
       <c r="Q72" s="74">
         <f t="shared" si="25"/>
-        <v>1485.3</v>
+        <v>1673.3</v>
       </c>
       <c r="R72" s="44">
         <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="61"/>
       <c r="B73" s="78" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C73" s="61">
         <v>31</v>
       </c>
       <c r="D73" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E73" s="79"/>
       <c r="F73" s="80">
@@ -7830,7 +7840,7 @@
       </c>
       <c r="M73" s="127">
         <f t="shared" si="23"/>
-        <v>248.20603199999999</v>
+        <v>429.41520000000003</v>
       </c>
       <c r="N73" s="127">
         <f t="shared" si="24"/>
@@ -7842,27 +7852,27 @@
       </c>
       <c r="P73" s="73">
         <f t="shared" si="28"/>
-        <v>7279.31</v>
+        <v>7460.31</v>
       </c>
       <c r="Q73" s="74">
         <f t="shared" si="25"/>
-        <v>7497.31</v>
+        <v>7684.31</v>
       </c>
       <c r="R73" s="44">
         <f t="shared" si="29"/>
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="61"/>
       <c r="B74" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C74" s="61">
         <v>32</v>
       </c>
       <c r="D74" s="79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E74" s="79"/>
       <c r="F74" s="80">
@@ -7890,7 +7900,7 @@
       </c>
       <c r="M74" s="127">
         <f t="shared" si="23"/>
-        <v>19608.276528000002</v>
+        <v>33923.800800000005</v>
       </c>
       <c r="N74" s="127">
         <f t="shared" si="24"/>
@@ -7902,27 +7912,27 @@
       </c>
       <c r="P74" s="73">
         <f t="shared" si="28"/>
-        <v>2619346.3199999998</v>
+        <v>2633662.3199999998</v>
       </c>
       <c r="Q74" s="74">
         <f t="shared" si="25"/>
-        <v>2697926.32</v>
+        <v>2712672.32</v>
       </c>
       <c r="R74" s="44">
         <f t="shared" si="29"/>
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="61"/>
       <c r="B75" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C75" s="61">
         <v>1</v>
       </c>
       <c r="D75" s="79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E75" s="79"/>
       <c r="F75" s="80">
@@ -7950,7 +7960,7 @@
       </c>
       <c r="M75" s="127">
         <f t="shared" si="23"/>
-        <v>7570.2839759999997</v>
+        <v>13097.163600000002</v>
       </c>
       <c r="N75" s="127">
         <f t="shared" si="24"/>
@@ -7962,27 +7972,27 @@
       </c>
       <c r="P75" s="73">
         <f t="shared" si="28"/>
-        <v>340121.01</v>
+        <v>345648.01</v>
       </c>
       <c r="Q75" s="74">
         <f t="shared" si="25"/>
-        <v>350325.01</v>
+        <v>356017.01</v>
       </c>
       <c r="R75" s="44">
         <f t="shared" si="29"/>
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
       <c r="B76" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C76" s="61">
         <v>2</v>
       </c>
       <c r="D76" s="79" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E76" s="79"/>
       <c r="F76" s="80">
@@ -8013,7 +8023,7 @@
       </c>
       <c r="M76" s="127">
         <f t="shared" si="23"/>
-        <v>7942.5930239999998</v>
+        <v>13741.286400000001</v>
       </c>
       <c r="N76" s="127">
         <f t="shared" si="24"/>
@@ -8025,27 +8035,27 @@
       </c>
       <c r="P76" s="73">
         <f t="shared" si="28"/>
-        <v>46160.02</v>
+        <v>51959.02</v>
       </c>
       <c r="Q76" s="74">
         <f t="shared" si="25"/>
-        <v>47545.02</v>
+        <v>53518.02</v>
       </c>
       <c r="R76" s="44">
         <f t="shared" si="29"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="61"/>
       <c r="B77" s="78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C77" s="61">
         <v>3</v>
       </c>
       <c r="D77" s="79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E77" s="79"/>
       <c r="F77" s="80">
@@ -8076,7 +8086,7 @@
       </c>
       <c r="M77" s="127">
         <f t="shared" si="23"/>
-        <v>7073.8719119999996</v>
+        <v>12238.333200000001</v>
       </c>
       <c r="N77" s="127">
         <f t="shared" si="24"/>
@@ -8088,27 +8098,27 @@
       </c>
       <c r="P77" s="73">
         <f t="shared" si="28"/>
-        <v>41111.03</v>
+        <v>46276.03</v>
       </c>
       <c r="Q77" s="74">
         <f t="shared" si="25"/>
-        <v>42344.03</v>
+        <v>47664.03</v>
       </c>
       <c r="R77" s="44">
         <f t="shared" si="29"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="61"/>
       <c r="B78" s="78" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C78" s="61">
         <v>4</v>
       </c>
       <c r="D78" s="79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E78" s="79"/>
       <c r="F78" s="80">
@@ -8139,7 +8149,7 @@
       </c>
       <c r="M78" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N78" s="127">
         <f t="shared" si="24"/>
@@ -8151,30 +8161,30 @@
       </c>
       <c r="P78" s="73">
         <f t="shared" si="28"/>
-        <v>38226.04</v>
+        <v>43028.04</v>
       </c>
       <c r="Q78" s="74">
         <f t="shared" si="25"/>
-        <v>39373.040000000001</v>
+        <v>44319.040000000001</v>
       </c>
       <c r="R78" s="44">
         <f t="shared" si="29"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="61"/>
       <c r="B79" s="78" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C79" s="61">
         <v>5</v>
       </c>
       <c r="D79" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" s="60" t="s">
         <v>90</v>
-      </c>
-      <c r="E79" s="60" t="s">
-        <v>91</v>
       </c>
       <c r="F79" s="80">
         <v>5.3E-3</v>
@@ -8204,7 +8214,7 @@
       </c>
       <c r="M79" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N79" s="127">
         <f t="shared" si="24"/>
@@ -8216,30 +8226,30 @@
       </c>
       <c r="P79" s="73">
         <f t="shared" si="28"/>
-        <v>38226.050000000003</v>
+        <v>43028.05</v>
       </c>
       <c r="Q79" s="74">
         <f t="shared" si="25"/>
-        <v>39373.050000000003</v>
+        <v>44319.05</v>
       </c>
       <c r="R79" s="44">
         <f t="shared" si="29"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="61"/>
       <c r="B80" s="78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C80" s="61">
         <v>6</v>
       </c>
       <c r="D80" s="79" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E80" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F80" s="80">
         <v>5.3E-3</v>
@@ -8269,7 +8279,7 @@
       </c>
       <c r="M80" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N80" s="127">
         <f t="shared" si="24"/>
@@ -8281,35 +8291,35 @@
       </c>
       <c r="P80" s="73">
         <f t="shared" si="28"/>
-        <v>38226.06</v>
+        <v>43028.06</v>
       </c>
       <c r="Q80" s="74">
         <f t="shared" si="25"/>
-        <v>39373.06</v>
+        <v>44319.06</v>
       </c>
       <c r="R80" s="44">
         <f t="shared" si="29"/>
         <v>0.06</v>
       </c>
       <c r="S80" s="176" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="61">
         <v>12</v>
       </c>
       <c r="B81" s="78" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C81" s="61">
         <v>7</v>
       </c>
       <c r="D81" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="E81" s="75" t="s">
         <v>153</v>
-      </c>
-      <c r="E81" s="75" t="s">
-        <v>154</v>
       </c>
       <c r="F81" s="80">
         <v>5.3E-3</v>
@@ -8339,7 +8349,7 @@
       </c>
       <c r="M81" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N81" s="127">
         <f t="shared" si="24"/>
@@ -8351,29 +8361,29 @@
       </c>
       <c r="P81" s="73">
         <f t="shared" si="28"/>
-        <v>38226.07</v>
+        <v>43028.07</v>
       </c>
       <c r="Q81" s="74">
         <f t="shared" si="25"/>
-        <v>39373.07</v>
+        <v>44319.07</v>
       </c>
       <c r="R81" s="44">
         <f t="shared" si="29"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="61">
         <v>12</v>
       </c>
       <c r="B82" s="77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C82" s="61">
         <v>8</v>
       </c>
       <c r="D82" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E82" s="179"/>
       <c r="F82" s="80">
@@ -8401,7 +8411,7 @@
       </c>
       <c r="M82" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N82" s="127">
         <f t="shared" si="24"/>
@@ -8413,29 +8423,29 @@
       </c>
       <c r="P82" s="73">
         <f t="shared" si="28"/>
-        <v>192869.08</v>
+        <v>197671.08</v>
       </c>
       <c r="Q82" s="74">
         <f t="shared" si="25"/>
-        <v>198655.08</v>
+        <v>203601.08</v>
       </c>
       <c r="R82" s="44">
         <f t="shared" si="29"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="61">
         <v>12</v>
       </c>
       <c r="B83" s="77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C83" s="61">
         <v>9</v>
       </c>
       <c r="D83" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E83" s="79" t="str">
         <f>E44</f>
@@ -8466,7 +8476,7 @@
       </c>
       <c r="M83" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N83" s="127">
         <f t="shared" si="24"/>
@@ -8478,27 +8488,27 @@
       </c>
       <c r="P83" s="73">
         <f t="shared" si="28"/>
-        <v>123624.09</v>
+        <v>128426.09</v>
       </c>
       <c r="Q83" s="74">
         <f t="shared" si="25"/>
-        <v>127333.09</v>
+        <v>132279.09</v>
       </c>
       <c r="R83" s="44">
         <f t="shared" si="29"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="61"/>
       <c r="B84" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C84" s="77">
         <v>10</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E84" s="75"/>
       <c r="F84" s="69">
@@ -8526,7 +8536,7 @@
       </c>
       <c r="M84" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N84" s="127">
         <f t="shared" si="24"/>
@@ -8538,30 +8548,30 @@
       </c>
       <c r="P84" s="73">
         <f t="shared" si="28"/>
-        <v>292057.09999999998</v>
+        <v>296859.09999999998</v>
       </c>
       <c r="Q84" s="74">
         <f t="shared" si="25"/>
-        <v>300819.09999999998</v>
+        <v>305765.09999999998</v>
       </c>
       <c r="R84" s="44">
         <f t="shared" si="29"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="61"/>
       <c r="B85" s="77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C85" s="77">
         <v>11</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E85" s="75" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F85" s="69">
         <v>5.3E-3</v>
@@ -8591,7 +8601,7 @@
       </c>
       <c r="M85" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N85" s="127">
         <f t="shared" si="24"/>
@@ -8603,30 +8613,30 @@
       </c>
       <c r="P85" s="73">
         <f t="shared" si="28"/>
-        <v>117437.11</v>
+        <v>122239.11</v>
       </c>
       <c r="Q85" s="74">
         <f t="shared" si="25"/>
-        <v>120960.11</v>
+        <v>125906.11</v>
       </c>
       <c r="R85" s="44">
         <f t="shared" si="29"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="61"/>
       <c r="B86" s="77" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="77">
         <v>12</v>
       </c>
       <c r="D86" s="180" t="s">
+        <v>121</v>
+      </c>
+      <c r="E86" s="60" t="s">
         <v>122</v>
-      </c>
-      <c r="E86" s="60" t="s">
-        <v>123</v>
       </c>
       <c r="F86" s="69">
         <v>5.3E-3</v>
@@ -8656,7 +8666,7 @@
       </c>
       <c r="M86" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N86" s="127">
         <f t="shared" si="24"/>
@@ -8668,27 +8678,27 @@
       </c>
       <c r="P86" s="73">
         <f t="shared" si="28"/>
-        <v>38226.120000000003</v>
+        <v>43028.12</v>
       </c>
       <c r="Q86" s="74">
         <f t="shared" si="25"/>
-        <v>39373.120000000003</v>
+        <v>44319.12</v>
       </c>
       <c r="R86" s="44">
         <f t="shared" si="29"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="61"/>
       <c r="B87" s="61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C87" s="61">
         <v>13</v>
       </c>
       <c r="D87" s="180" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E87" s="75"/>
       <c r="F87" s="69">
@@ -8719,7 +8729,7 @@
       </c>
       <c r="M87" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N87" s="127">
         <f t="shared" si="24"/>
@@ -8731,30 +8741,30 @@
       </c>
       <c r="P87" s="73">
         <f t="shared" si="28"/>
-        <v>38226.129999999997</v>
+        <v>43028.13</v>
       </c>
       <c r="Q87" s="74">
         <f t="shared" si="25"/>
-        <v>39373.129999999997</v>
+        <v>44319.13</v>
       </c>
       <c r="R87" s="44">
         <f t="shared" si="29"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="61"/>
       <c r="B88" s="61" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C88" s="61">
         <v>14</v>
       </c>
       <c r="D88" s="180" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E88" s="75" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F88" s="69">
         <v>5.3E-3</v>
@@ -8784,7 +8794,7 @@
       </c>
       <c r="M88" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N88" s="127">
         <f t="shared" si="24"/>
@@ -8796,27 +8806,27 @@
       </c>
       <c r="P88" s="73">
         <f t="shared" si="28"/>
-        <v>29456.14</v>
+        <v>34258.14</v>
       </c>
       <c r="Q88" s="74">
         <f t="shared" si="25"/>
-        <v>30340.14</v>
+        <v>35286.14</v>
       </c>
       <c r="R88" s="44">
         <f t="shared" si="29"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="61"/>
       <c r="B89" s="61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C89" s="61">
         <v>15</v>
       </c>
       <c r="D89" s="180" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E89" s="75" t="str">
         <f>E20</f>
@@ -8850,7 +8860,7 @@
       </c>
       <c r="M89" s="127">
         <f t="shared" si="23"/>
-        <v>6577.4598479999995</v>
+        <v>11379.5028</v>
       </c>
       <c r="N89" s="127">
         <f t="shared" si="24"/>
@@ -8862,30 +8872,30 @@
       </c>
       <c r="P89" s="73">
         <f t="shared" si="28"/>
-        <v>38226.15</v>
+        <v>43028.15</v>
       </c>
       <c r="Q89" s="74">
         <f t="shared" si="25"/>
-        <v>39373.15</v>
+        <v>44319.15</v>
       </c>
       <c r="R89" s="44">
         <f t="shared" si="29"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="60"/>
       <c r="B90" s="60" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C90" s="61">
         <v>16</v>
       </c>
       <c r="D90" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E90" s="60" t="s">
         <v>142</v>
-      </c>
-      <c r="E90" s="60" t="s">
-        <v>143</v>
       </c>
       <c r="F90" s="69">
         <v>6.1999999999999998E-3</v>
@@ -8915,7 +8925,7 @@
       </c>
       <c r="M90" s="127">
         <f t="shared" si="23"/>
-        <v>7694.3869919999988</v>
+        <v>13311.8712</v>
       </c>
       <c r="N90" s="127">
         <f t="shared" si="24"/>
@@ -8927,18 +8937,18 @@
       </c>
       <c r="P90" s="73">
         <f t="shared" si="28"/>
-        <v>44717.16</v>
+        <v>50335.16</v>
       </c>
       <c r="Q90" s="74">
         <f t="shared" si="25"/>
-        <v>46059.16</v>
+        <v>51845.16</v>
       </c>
       <c r="R90" s="44">
         <f t="shared" si="29"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="61"/>
       <c r="B91" s="141"/>
       <c r="C91" s="141"/>
@@ -8958,7 +8968,7 @@
       <c r="Q91" s="164"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="81"/>
       <c r="B92" s="165"/>
       <c r="C92" s="166"/>
@@ -8994,7 +9004,7 @@
       </c>
       <c r="M92" s="173">
         <f>SUM(M5:M90)</f>
-        <v>1241030.1599999997</v>
+        <v>2147075.9999999967</v>
       </c>
       <c r="N92" s="173">
         <f>SUM(N5:N90)</f>
@@ -9006,122 +9016,115 @@
       </c>
       <c r="P92" s="174">
         <f>SUM(P5:P91)</f>
-        <v>13307357.699999997</v>
+        <v>14213407.699999997</v>
       </c>
       <c r="Q92" s="174">
         <f>SUM(Q5:Q91)</f>
-        <v>13706588.699999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+        <v>14639807.699999997</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="H94" s="120"/>
     </row>
-    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="197" t="str">
+    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D95" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E95" s="192"/>
-      <c r="F95" s="192"/>
-      <c r="G95" s="192"/>
-      <c r="H95" s="192"/>
-      <c r="I95" s="192"/>
-      <c r="J95" s="192"/>
-      <c r="K95" s="192"/>
-      <c r="L95" s="192"/>
-      <c r="M95" s="192"/>
-      <c r="N95" s="192"/>
-      <c r="O95" s="192"/>
-      <c r="P95" s="192"/>
-    </row>
-    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="192"/>
-      <c r="E96" s="192"/>
-      <c r="F96" s="192"/>
-      <c r="G96" s="192"/>
-      <c r="H96" s="192"/>
-      <c r="I96" s="192"/>
-      <c r="J96" s="192"/>
-      <c r="K96" s="192"/>
-      <c r="L96" s="192"/>
-      <c r="M96" s="192"/>
-      <c r="N96" s="192"/>
-      <c r="O96" s="192"/>
-      <c r="P96" s="192"/>
-    </row>
-    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="192"/>
-      <c r="E97" s="192"/>
-      <c r="F97" s="192"/>
-      <c r="G97" s="192"/>
-      <c r="H97" s="192"/>
-      <c r="I97" s="192"/>
-      <c r="J97" s="192"/>
-      <c r="K97" s="192"/>
-      <c r="L97" s="192"/>
-      <c r="M97" s="192"/>
-      <c r="N97" s="192"/>
-      <c r="O97" s="192"/>
-      <c r="P97" s="192"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="192"/>
-      <c r="E98" s="192"/>
-      <c r="F98" s="192"/>
-      <c r="G98" s="192"/>
-      <c r="H98" s="192"/>
-      <c r="I98" s="192"/>
-      <c r="J98" s="192"/>
-      <c r="K98" s="192"/>
-      <c r="L98" s="192"/>
-      <c r="M98" s="192"/>
-      <c r="N98" s="192"/>
-      <c r="O98" s="192"/>
-      <c r="P98" s="192"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="192"/>
-      <c r="E99" s="192"/>
-      <c r="F99" s="192"/>
-      <c r="G99" s="192"/>
-      <c r="H99" s="192"/>
-      <c r="I99" s="192"/>
-      <c r="J99" s="192"/>
-      <c r="K99" s="192"/>
-      <c r="L99" s="192"/>
-      <c r="M99" s="192"/>
-      <c r="N99" s="192"/>
-      <c r="O99" s="192"/>
-      <c r="P99" s="192"/>
-    </row>
-    <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="192"/>
-      <c r="E100" s="192"/>
-      <c r="F100" s="192"/>
-      <c r="G100" s="192"/>
-      <c r="H100" s="192"/>
-      <c r="I100" s="192"/>
-      <c r="J100" s="192"/>
-      <c r="K100" s="192"/>
-      <c r="L100" s="192"/>
-      <c r="M100" s="192"/>
-      <c r="N100" s="192"/>
-      <c r="O100" s="192"/>
-      <c r="P100" s="192"/>
+      <c r="E95" s="190"/>
+      <c r="F95" s="190"/>
+      <c r="G95" s="190"/>
+      <c r="H95" s="190"/>
+      <c r="I95" s="190"/>
+      <c r="J95" s="190"/>
+      <c r="K95" s="190"/>
+      <c r="L95" s="190"/>
+      <c r="M95" s="190"/>
+      <c r="N95" s="190"/>
+      <c r="O95" s="190"/>
+      <c r="P95" s="190"/>
+    </row>
+    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="190"/>
+      <c r="E96" s="190"/>
+      <c r="F96" s="190"/>
+      <c r="G96" s="190"/>
+      <c r="H96" s="190"/>
+      <c r="I96" s="190"/>
+      <c r="J96" s="190"/>
+      <c r="K96" s="190"/>
+      <c r="L96" s="190"/>
+      <c r="M96" s="190"/>
+      <c r="N96" s="190"/>
+      <c r="O96" s="190"/>
+      <c r="P96" s="190"/>
+    </row>
+    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D97" s="190"/>
+      <c r="E97" s="190"/>
+      <c r="F97" s="190"/>
+      <c r="G97" s="190"/>
+      <c r="H97" s="190"/>
+      <c r="I97" s="190"/>
+      <c r="J97" s="190"/>
+      <c r="K97" s="190"/>
+      <c r="L97" s="190"/>
+      <c r="M97" s="190"/>
+      <c r="N97" s="190"/>
+      <c r="O97" s="190"/>
+      <c r="P97" s="190"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D98" s="190"/>
+      <c r="E98" s="190"/>
+      <c r="F98" s="190"/>
+      <c r="G98" s="190"/>
+      <c r="H98" s="190"/>
+      <c r="I98" s="190"/>
+      <c r="J98" s="190"/>
+      <c r="K98" s="190"/>
+      <c r="L98" s="190"/>
+      <c r="M98" s="190"/>
+      <c r="N98" s="190"/>
+      <c r="O98" s="190"/>
+      <c r="P98" s="190"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D99" s="190"/>
+      <c r="E99" s="190"/>
+      <c r="F99" s="190"/>
+      <c r="G99" s="190"/>
+      <c r="H99" s="190"/>
+      <c r="I99" s="190"/>
+      <c r="J99" s="190"/>
+      <c r="K99" s="190"/>
+      <c r="L99" s="190"/>
+      <c r="M99" s="190"/>
+      <c r="N99" s="190"/>
+      <c r="O99" s="190"/>
+      <c r="P99" s="190"/>
+    </row>
+    <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="190"/>
+      <c r="E100" s="190"/>
+      <c r="F100" s="190"/>
+      <c r="G100" s="190"/>
+      <c r="H100" s="190"/>
+      <c r="I100" s="190"/>
+      <c r="J100" s="190"/>
+      <c r="K100" s="190"/>
+      <c r="L100" s="190"/>
+      <c r="M100" s="190"/>
+      <c r="N100" s="190"/>
+      <c r="O100" s="190"/>
+      <c r="P100" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="D95:P100"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
@@ -9138,6 +9141,13 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D95:P100"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9147,57 +9157,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
   <dimension ref="D3:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D3" s="120"/>
     </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D4" s="120"/>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D5" s="120"/>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D6" s="120"/>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D7" s="120"/>
     </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D8" s="120"/>
     </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D9" s="120"/>
     </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D10" s="120"/>
     </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D11" s="120"/>
     </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D12" s="120" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D13" s="120"/>
     </row>
-    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D14" s="120"/>
     </row>
-    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="223" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D15" s="187" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" s="177" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D21" s="120"/>
       <c r="E21" s="120"/>
       <c r="F21" s="120"/>

--- a/VERGARA/Julio/vergara Julio.xlsx
+++ b/VERGARA/Julio/vergara Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BE57C4-FE47-4754-B4E0-318AD97F0B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5F2EE0-EDDA-4BF0-AD2E-372630DBF194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="286">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -820,9 +820,6 @@
   </si>
   <si>
     <t>Transf 13/06</t>
-  </si>
-  <si>
-    <t>Incluye SAC</t>
   </si>
   <si>
     <t>Tranfs 27/06</t>
@@ -896,15 +893,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1528,8 +1525,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1551,8 +1548,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1561,31 +1558,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1596,8 +1593,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1615,18 +1612,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1644,35 +1641,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1680,11 +1677,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1695,17 +1692,17 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1721,27 +1718,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1751,7 +1748,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1759,30 +1756,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1795,16 +1792,20 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1813,6 +1814,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1837,7 +1844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1855,16 +1862,20 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1872,27 +1883,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2254,20 +2251,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="66" t="s">
         <v>0</v>
@@ -2276,7 +2273,7 @@
       <c r="D1" s="66"/>
       <c r="E1" s="67"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="130" t="s">
         <v>1</v>
@@ -2285,7 +2282,7 @@
       <c r="D2" s="130"/>
       <c r="E2" s="68"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
       <c r="B3" s="131" t="s">
         <v>2</v>
@@ -2296,7 +2293,7 @@
       </c>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2307,18 +2304,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="199" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="198"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="205" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="204"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2329,57 +2326,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="200" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="190"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="190"/>
-      <c r="C10" s="190"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="201" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="202"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="202"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
-      <c r="B15" s="202"/>
-      <c r="C15" s="202"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="202"/>
-      <c r="B16" s="202"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="206" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="194"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="194"/>
+      <c r="C9" s="194"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="207" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2388,7 +2385,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
@@ -2397,44 +2394,42 @@
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="182">
-        <v>1033560</v>
-      </c>
-      <c r="E22" s="86" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="191">
+        <v>612874.4</v>
+      </c>
+      <c r="E22" s="86"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="182">
-        <v>-224799.3</v>
+      <c r="D23" s="191">
+        <v>-143013.39000000001</v>
       </c>
       <c r="E23" s="86"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="182">
-        <v>0.3</v>
+      <c r="D24" s="191">
+        <v>0.99</v>
       </c>
       <c r="E24" s="86"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
         <v>14</v>
       </c>
@@ -2442,12 +2437,12 @@
       <c r="C25" s="55"/>
       <c r="D25" s="114">
         <f>SUM(D22:D24)</f>
-        <v>808761</v>
+        <v>469862</v>
       </c>
       <c r="E25" s="87"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>15</v>
       </c>
@@ -2456,11 +2451,11 @@
       <c r="D26" s="27"/>
       <c r="E26" s="88">
         <f>D25</f>
-        <v>808761</v>
+        <v>469862</v>
       </c>
       <c r="F26" s="19"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>16</v>
       </c>
@@ -2469,26 +2464,26 @@
       <c r="D27" s="33"/>
       <c r="E27" s="89"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="191" t="s">
-        <v>280</v>
-      </c>
-      <c r="B28" s="192"/>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="195" t="s">
+        <v>279</v>
+      </c>
+      <c r="B28" s="196"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="228">
+      <c r="D28" s="191">
         <v>35000</v>
       </c>
       <c r="E28" s="90" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="191" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="192"/>
+    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="195" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" s="196"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="182">
+      <c r="D29" s="192">
         <f>470000*2</f>
         <v>940000</v>
       </c>
@@ -2496,7 +2491,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>17</v>
       </c>
@@ -2508,7 +2503,7 @@
         <v>975000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
         <v>18</v>
       </c>
@@ -2517,30 +2512,30 @@
       <c r="D31" s="34"/>
       <c r="E31" s="65"/>
     </row>
-    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="154" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="148"/>
       <c r="C32" s="53"/>
-      <c r="D32" s="183">
+      <c r="D32" s="182">
         <v>70868</v>
       </c>
       <c r="E32" s="113"/>
       <c r="G32" s="153"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="191" t="s">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="195" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="192"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="53"/>
       <c r="D33" s="181">
         <v>719.9</v>
       </c>
       <c r="E33" s="113"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>21</v>
       </c>
@@ -2552,7 +2547,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="32" t="s">
         <v>22</v>
       </c>
@@ -2561,7 +2556,7 @@
       <c r="D35" s="37"/>
       <c r="E35" s="93"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>23</v>
       </c>
@@ -2575,22 +2570,22 @@
       </c>
       <c r="G36" s="120"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="224">
+      <c r="D37" s="189">
         <v>45243</v>
       </c>
       <c r="E37" s="101" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="str">
         <f>A37</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2599,7 +2594,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="5"/>
-      <c r="D38" s="224">
+      <c r="D38" s="189">
         <v>83582.350000000006</v>
       </c>
       <c r="E38" s="101" t="str">
@@ -2607,7 +2602,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="str">
         <f>A38</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2616,7 +2611,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="224">
+      <c r="D39" s="189">
         <v>5027</v>
       </c>
       <c r="E39" s="102" t="str">
@@ -2624,7 +2619,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>27</v>
       </c>
@@ -2636,7 +2631,7 @@
         <v>600113.1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
         <v>28</v>
       </c>
@@ -2645,7 +2640,7 @@
       <c r="D41" s="37"/>
       <c r="E41" s="93"/>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>29</v>
       </c>
@@ -2659,7 +2654,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>30</v>
       </c>
@@ -2669,14 +2664,14 @@
         <v>50000</v>
       </c>
       <c r="E43" s="99" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="191" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="195" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="192"/>
+      <c r="B44" s="196"/>
       <c r="C44" s="5"/>
       <c r="D44" s="181">
         <v>84984.35</v>
@@ -2685,7 +2680,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
         <v>32</v>
       </c>
@@ -2697,7 +2692,7 @@
         <v>304243.27</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
         <v>33</v>
       </c>
@@ -2706,9 +2701,9 @@
       <c r="D46" s="36"/>
       <c r="E46" s="95"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="149" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B47" s="150"/>
       <c r="C47" s="63"/>
@@ -2716,27 +2711,27 @@
         <v>38950</v>
       </c>
       <c r="E47" s="151" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="195" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="191" t="s">
-        <v>266</v>
-      </c>
-      <c r="B48" s="192"/>
+      <c r="B48" s="196"/>
       <c r="C48" s="54"/>
       <c r="D48" s="181">
         <v>110000</v>
       </c>
       <c r="E48" s="151" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="194" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="200" t="s">
         <v>253</v>
       </c>
-      <c r="B49" s="195"/>
+      <c r="B49" s="201"/>
       <c r="C49" s="54"/>
       <c r="D49" s="181">
         <v>110000</v>
@@ -2745,11 +2740,11 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="191" t="s">
+    <row r="50" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="195" t="s">
         <v>256</v>
       </c>
-      <c r="B50" s="192"/>
+      <c r="B50" s="196"/>
       <c r="C50" s="54"/>
       <c r="D50" s="181">
         <v>135000</v>
@@ -2758,9 +2753,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="137" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B51" s="126"/>
       <c r="C51" s="54"/>
@@ -2768,52 +2763,52 @@
         <v>25000</v>
       </c>
       <c r="E51" s="151" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="191" t="s">
-        <v>286</v>
-      </c>
-      <c r="B52" s="192"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="195" t="s">
+        <v>285</v>
+      </c>
+      <c r="B52" s="196"/>
       <c r="C52" s="54"/>
-      <c r="D52" s="224">
+      <c r="D52" s="189">
         <v>16500</v>
       </c>
       <c r="E52" s="152" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="222" t="s">
         <v>284</v>
       </c>
-      <c r="B53" s="223"/>
+    </row>
+    <row r="53" spans="1:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="197" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" s="198"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="224">
+      <c r="D53" s="189">
         <v>60000</v>
       </c>
       <c r="E53" s="152" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="191" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="195" t="s">
         <v>255</v>
       </c>
-      <c r="B54" s="192"/>
+      <c r="B54" s="196"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="221">
+      <c r="D54" s="188">
         <f>60650+58080</f>
         <v>118730</v>
       </c>
-      <c r="E54" s="225" t="s">
-        <v>283</v>
-      </c>
-      <c r="I54" s="191"/>
-      <c r="J54" s="192"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E54" s="190" t="s">
+        <v>282</v>
+      </c>
+      <c r="I54" s="195"/>
+      <c r="J54" s="196"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>35</v>
       </c>
@@ -2825,7 +2820,7 @@
         <v>614180</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
         <v>36</v>
       </c>
@@ -2834,7 +2829,7 @@
       <c r="D56" s="27"/>
       <c r="E56" s="95"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>37</v>
       </c>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="E57" s="103"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>38</v>
       </c>
@@ -2856,7 +2851,7 @@
       </c>
       <c r="E58" s="100"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="51" t="s">
         <v>17</v>
       </c>
@@ -2868,14 +2863,14 @@
         <v>159752.69</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="86"/>
       <c r="E60" s="105"/>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="28" t="s">
         <v>39</v>
       </c>
@@ -2884,14 +2879,14 @@
       <c r="D61" s="106"/>
       <c r="E61" s="136"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="D62" s="107"/>
       <c r="E62" s="108"/>
       <c r="F62" s="44"/>
       <c r="G62" s="143"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
@@ -2900,19 +2895,19 @@
       <c r="D63" s="109"/>
       <c r="E63" s="135">
         <f>(SUM(E26:E61))</f>
-        <v>3533637.96</v>
+        <v>3194738.96</v>
       </c>
       <c r="F63" s="134"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D64" s="107"/>
       <c r="E64" s="107"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D65" s="107"/>
       <c r="E65" s="107"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>41</v>
       </c>
@@ -2921,11 +2916,11 @@
       <c r="D66" s="110"/>
       <c r="E66" s="111"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="191" t="s">
-        <v>271</v>
-      </c>
-      <c r="B67" s="192"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="195" t="s">
+        <v>270</v>
+      </c>
+      <c r="B67" s="196"/>
       <c r="C67" s="5"/>
       <c r="D67" s="97">
         <f>2*304993.06</f>
@@ -2935,14 +2930,14 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="96"/>
       <c r="B68" s="98"/>
       <c r="C68" s="5"/>
       <c r="D68" s="97"/>
       <c r="E68" s="94"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="49"/>
       <c r="B69" s="48"/>
       <c r="C69" s="48"/>
@@ -2952,19 +2947,19 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="196" t="s">
+    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="197"/>
-      <c r="C72" s="197"/>
-      <c r="D72" s="198"/>
+      <c r="B72" s="203"/>
+      <c r="C72" s="203"/>
+      <c r="D72" s="204"/>
       <c r="E72" s="144"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>43</v>
       </c>
@@ -2976,26 +2971,26 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="83" t="s">
         <v>44</v>
       </c>
       <c r="B76" s="84">
         <f>E63</f>
-        <v>3533637.96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3194738.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="83" t="s">
         <v>45</v>
       </c>
       <c r="B77" s="84">
         <f>E63-E61</f>
-        <v>3533637.96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3194738.96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="83" t="s">
         <v>46</v>
       </c>
@@ -3004,7 +2999,7 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="83" t="s">
         <v>47</v>
       </c>
@@ -3013,15 +3008,15 @@
         <v>609986.12</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="45" t="s">
         <v>48</v>
       </c>
       <c r="B81" s="121"/>
       <c r="C81" s="20"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
         <v>49</v>
       </c>
@@ -3030,7 +3025,7 @@
       </c>
       <c r="C82" s="22"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="21" t="s">
         <v>50</v>
       </c>
@@ -3040,7 +3035,7 @@
       </c>
       <c r="C83" s="20"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
         <v>51</v>
       </c>
@@ -3050,7 +3045,7 @@
       </c>
       <c r="C84" s="20"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="116" t="s">
         <v>52</v>
       </c>
@@ -3060,17 +3055,17 @@
       </c>
       <c r="C85" s="20"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="40" t="s">
         <v>53</v>
       </c>
       <c r="B86" s="47">
         <f>-B77</f>
-        <v>-3533637.96</v>
+        <v>-3194738.96</v>
       </c>
       <c r="C86" s="20"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
         <v>54</v>
       </c>
@@ -3080,7 +3075,7 @@
       </c>
       <c r="C87" s="20"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="40" t="s">
         <v>55</v>
       </c>
@@ -3090,7 +3085,7 @@
       </c>
       <c r="C88" s="20"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="s">
         <v>56</v>
       </c>
@@ -3100,63 +3095,63 @@
       </c>
       <c r="C89" s="20"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="124" t="s">
         <v>35</v>
       </c>
       <c r="B90" s="125">
         <f>SUM(B82:B89)</f>
-        <v>-179668.93000000168</v>
+        <v>159230.06999999832</v>
       </c>
       <c r="C90" s="23"/>
       <c r="D90" s="44"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B91" s="42"/>
       <c r="C91" s="23"/>
       <c r="D91" s="44"/>
       <c r="E91" s="122"/>
       <c r="F91" s="123"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B92" s="42"/>
       <c r="C92" s="23"/>
       <c r="D92" s="44"/>
       <c r="E92" s="122"/>
       <c r="F92" s="123"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="193" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="199" t="s">
         <v>57</v>
       </c>
-      <c r="B93" s="190"/>
-      <c r="C93" s="190"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="190"/>
-      <c r="B94" s="190"/>
-      <c r="C94" s="190"/>
-    </row>
-    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="194"/>
+      <c r="C93" s="194"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="194"/>
+      <c r="B94" s="194"/>
+      <c r="C94" s="194"/>
+    </row>
+    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="53"/>
       <c r="B95" s="139"/>
       <c r="C95" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="53"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
     </row>
-    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="128"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
         <v>35</v>
       </c>
@@ -3166,36 +3161,36 @@
       </c>
       <c r="C98" s="46"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="189"/>
-      <c r="B100" s="190"/>
-      <c r="C100" s="190"/>
-      <c r="D100" s="190"/>
-      <c r="E100" s="190"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="190"/>
-      <c r="B101" s="190"/>
-      <c r="C101" s="190"/>
-      <c r="D101" s="190"/>
-      <c r="E101" s="190"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="190"/>
-      <c r="B102" s="190"/>
-      <c r="C102" s="190"/>
-      <c r="D102" s="190"/>
-      <c r="E102" s="190"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="190"/>
-      <c r="B103" s="190"/>
-      <c r="C103" s="190"/>
-      <c r="D103" s="190"/>
-      <c r="E103" s="190"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="193"/>
+      <c r="B100" s="194"/>
+      <c r="C100" s="194"/>
+      <c r="D100" s="194"/>
+      <c r="E100" s="194"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="194"/>
+      <c r="B101" s="194"/>
+      <c r="C101" s="194"/>
+      <c r="D101" s="194"/>
+      <c r="E101" s="194"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="194"/>
+      <c r="B102" s="194"/>
+      <c r="C102" s="194"/>
+      <c r="D102" s="194"/>
+      <c r="E102" s="194"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="194"/>
+      <c r="B103" s="194"/>
+      <c r="C103" s="194"/>
+      <c r="D103" s="194"/>
+      <c r="E103" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3227,27 +3222,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="11" width="9.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3255,30 +3250,30 @@
       <c r="E1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="226">
+      <c r="F1" s="221">
         <v>2147076</v>
       </c>
-      <c r="G1" s="227"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="185" t="s">
+      <c r="G1" s="222"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="184" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="184"/>
-      <c r="M1" s="212">
+      <c r="L1" s="183"/>
+      <c r="M1" s="218">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="213"/>
+      <c r="N1" s="219"/>
       <c r="O1" s="138"/>
-      <c r="P1" s="211">
+      <c r="P1" s="217">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="190"/>
+      <c r="Q1" s="194"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3286,106 +3281,106 @@
       <c r="E2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="203">
+      <c r="F2" s="209">
         <v>561462.80000000005</v>
       </c>
-      <c r="G2" s="204"/>
-      <c r="H2" s="184" t="s">
+      <c r="G2" s="210"/>
+      <c r="H2" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="214">
+      <c r="I2" s="220">
         <v>1200000</v>
       </c>
-      <c r="J2" s="204"/>
-      <c r="K2" s="184" t="s">
+      <c r="J2" s="210"/>
+      <c r="K2" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="184"/>
-      <c r="M2" s="214">
+      <c r="L2" s="183"/>
+      <c r="M2" s="220">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="210"/>
       <c r="O2" s="140"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="219"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="215" t="s">
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="223" t="s">
         <v>63</v>
       </c>
       <c r="B3" s="117"/>
-      <c r="C3" s="205" t="s">
+      <c r="C3" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="205" t="s">
+      <c r="D3" s="211" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="210" t="s">
+      <c r="E3" s="216" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="205" t="s">
+      <c r="F3" s="211" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="207" t="s">
+      <c r="G3" s="213" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="205" t="s">
+      <c r="H3" s="211" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="217" t="s">
+      <c r="I3" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="207" t="s">
+      <c r="J3" s="213" t="s">
         <v>70</v>
       </c>
-      <c r="K3" s="209" t="str">
+      <c r="K3" s="215" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="207" t="s">
+      <c r="L3" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="207" t="s">
+      <c r="M3" s="213" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="207" t="s">
+      <c r="N3" s="213" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="207" t="s">
+      <c r="O3" s="213" t="s">
         <v>74</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="Q3" s="220" t="s">
+      <c r="Q3" s="228" t="s">
         <v>76</v>
       </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="216"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="224"/>
       <c r="B4" s="118"/>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="206"/>
-      <c r="L4" s="208"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="214"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="Q4" s="206"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q4" s="212"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61"/>
       <c r="B5" s="61" t="s">
         <v>77</v>
@@ -3448,7 +3443,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="61"/>
       <c r="B6" s="61" t="s">
         <v>79</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
         <v>1</v>
       </c>
@@ -3577,7 +3572,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="61">
         <v>2</v>
       </c>
@@ -3643,7 +3638,7 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="61">
         <v>3</v>
       </c>
@@ -3711,7 +3706,7 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="61">
         <v>4</v>
       </c>
@@ -3724,7 +3719,7 @@
       <c r="D10" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="186" t="s">
+      <c r="E10" s="185" t="s">
         <v>90</v>
       </c>
       <c r="F10" s="69">
@@ -3778,7 +3773,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="61">
         <v>5</v>
       </c>
@@ -3843,7 +3838,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="61">
         <v>6</v>
       </c>
@@ -3908,7 +3903,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="61">
         <v>7</v>
       </c>
@@ -3975,7 +3970,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>8</v>
       </c>
@@ -4042,7 +4037,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>1</v>
       </c>
@@ -4109,7 +4104,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
         <v>1</v>
       </c>
@@ -4176,7 +4171,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61">
         <v>2</v>
       </c>
@@ -4243,7 +4238,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="61">
         <v>2</v>
       </c>
@@ -4311,7 +4306,7 @@
       </c>
       <c r="S18" s="120"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="61">
         <v>3</v>
       </c>
@@ -4379,7 +4374,7 @@
       </c>
       <c r="S19" s="120"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="61">
         <v>3</v>
       </c>
@@ -4448,7 +4443,7 @@
       <c r="S20" s="120"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>4</v>
       </c>
@@ -4515,7 +4510,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="61">
         <v>4</v>
       </c>
@@ -4577,7 +4572,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="61">
         <v>5</v>
       </c>
@@ -4641,7 +4636,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="61">
         <v>5</v>
       </c>
@@ -4708,7 +4703,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="61">
         <v>6</v>
       </c>
@@ -4773,7 +4768,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="61">
         <v>6</v>
       </c>
@@ -4840,7 +4835,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="61">
         <v>7</v>
       </c>
@@ -4907,7 +4902,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="61">
         <v>7</v>
       </c>
@@ -4974,7 +4969,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="61">
         <v>8</v>
       </c>
@@ -5039,7 +5034,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="61">
         <v>8</v>
       </c>
@@ -5106,7 +5101,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="61">
         <v>9</v>
       </c>
@@ -5168,7 +5163,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="61">
         <v>9</v>
       </c>
@@ -5235,7 +5230,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="61">
         <v>10</v>
       </c>
@@ -5300,7 +5295,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="61">
         <v>10</v>
       </c>
@@ -5367,7 +5362,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="61">
         <v>11</v>
       </c>
@@ -5434,7 +5429,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="61">
         <v>11</v>
       </c>
@@ -5501,7 +5496,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="61">
         <v>12</v>
       </c>
@@ -5568,7 +5563,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="61">
         <v>12</v>
       </c>
@@ -5635,7 +5630,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="61">
         <v>1</v>
       </c>
@@ -5702,7 +5697,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="61">
         <v>1</v>
       </c>
@@ -5770,7 +5765,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="60">
         <v>1</v>
       </c>
@@ -5836,7 +5831,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="61">
         <v>2</v>
       </c>
@@ -5903,7 +5898,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="61">
         <v>2</v>
       </c>
@@ -5970,7 +5965,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="61">
         <v>2</v>
       </c>
@@ -6034,7 +6029,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="61">
         <v>3</v>
       </c>
@@ -6098,7 +6093,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="61">
         <v>3</v>
       </c>
@@ -6165,7 +6160,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="61">
         <v>3</v>
       </c>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="T47" s="146"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="61">
         <v>4</v>
       </c>
@@ -6300,7 +6295,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="61">
         <v>4</v>
       </c>
@@ -6367,7 +6362,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="61">
         <v>4</v>
       </c>
@@ -6431,7 +6426,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="61">
         <v>5</v>
       </c>
@@ -6496,7 +6491,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="61">
         <v>5</v>
       </c>
@@ -6563,7 +6558,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="61">
         <v>5</v>
       </c>
@@ -6630,10 +6625,10 @@
         <v>0.81</v>
       </c>
       <c r="T53" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="61">
         <v>6</v>
       </c>
@@ -6698,7 +6693,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="61">
         <v>6</v>
       </c>
@@ -6762,7 +6757,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="61">
         <v>6</v>
       </c>
@@ -6827,7 +6822,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="61">
         <v>7</v>
       </c>
@@ -6863,7 +6858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="61">
         <v>7</v>
       </c>
@@ -6899,7 +6894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="61">
         <v>7</v>
       </c>
@@ -6966,7 +6961,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="61">
         <v>8</v>
       </c>
@@ -7028,7 +7023,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="61">
         <v>8</v>
       </c>
@@ -7090,7 +7085,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="61">
         <v>8</v>
       </c>
@@ -7101,7 +7096,7 @@
         <v>20</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
@@ -7154,7 +7149,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="61">
         <v>9</v>
       </c>
@@ -7221,7 +7216,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="61">
         <v>9</v>
       </c>
@@ -7286,7 +7281,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="61">
         <v>9</v>
       </c>
@@ -7353,7 +7348,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="61">
         <v>10</v>
       </c>
@@ -7418,7 +7413,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="61">
         <v>10</v>
       </c>
@@ -7485,7 +7480,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="61">
         <v>10</v>
       </c>
@@ -7498,7 +7493,7 @@
       <c r="D68" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E68" s="188"/>
+      <c r="E68" s="187"/>
       <c r="F68" s="76">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -7550,7 +7545,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="61">
         <v>11</v>
       </c>
@@ -7612,7 +7607,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="61">
         <v>11</v>
       </c>
@@ -7674,7 +7669,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="61">
         <v>11</v>
       </c>
@@ -7738,7 +7733,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="61"/>
       <c r="B72" s="78" t="s">
         <v>226</v>
@@ -7803,7 +7798,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="61"/>
       <c r="B73" s="78" t="s">
         <v>227</v>
@@ -7863,7 +7858,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="61"/>
       <c r="B74" s="78" t="s">
         <v>228</v>
@@ -7923,7 +7918,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="61"/>
       <c r="B75" s="78" t="s">
         <v>230</v>
@@ -7983,7 +7978,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="61"/>
       <c r="B76" s="78" t="s">
         <v>231</v>
@@ -8046,7 +8041,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="61"/>
       <c r="B77" s="78" t="s">
         <v>233</v>
@@ -8109,7 +8104,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="61"/>
       <c r="B78" s="78" t="s">
         <v>235</v>
@@ -8172,7 +8167,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="61"/>
       <c r="B79" s="78" t="s">
         <v>236</v>
@@ -8237,7 +8232,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="61"/>
       <c r="B80" s="78" t="s">
         <v>237</v>
@@ -8305,7 +8300,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="61">
         <v>12</v>
       </c>
@@ -8372,7 +8367,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="61">
         <v>12</v>
       </c>
@@ -8434,7 +8429,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="61">
         <v>12</v>
       </c>
@@ -8499,7 +8494,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="61"/>
       <c r="B84" s="77" t="s">
         <v>243</v>
@@ -8559,7 +8554,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="61"/>
       <c r="B85" s="77" t="s">
         <v>244</v>
@@ -8624,7 +8619,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="61"/>
       <c r="B86" s="77" t="s">
         <v>246</v>
@@ -8689,7 +8684,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="61"/>
       <c r="B87" s="61" t="s">
         <v>247</v>
@@ -8752,7 +8747,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="61"/>
       <c r="B88" s="61" t="s">
         <v>248</v>
@@ -8817,7 +8812,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="61"/>
       <c r="B89" s="61" t="s">
         <v>250</v>
@@ -8883,7 +8878,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="60"/>
       <c r="B90" s="60" t="s">
         <v>251</v>
@@ -8948,7 +8943,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="61"/>
       <c r="B91" s="141"/>
       <c r="C91" s="141"/>
@@ -8968,7 +8963,7 @@
       <c r="Q91" s="164"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="81"/>
       <c r="B92" s="165"/>
       <c r="C92" s="166"/>
@@ -9023,105 +9018,105 @@
         <v>14639807.699999997</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H94" s="120"/>
     </row>
-    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="189" t="str">
+    <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D95" s="193" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E95" s="190"/>
-      <c r="F95" s="190"/>
-      <c r="G95" s="190"/>
-      <c r="H95" s="190"/>
-      <c r="I95" s="190"/>
-      <c r="J95" s="190"/>
-      <c r="K95" s="190"/>
-      <c r="L95" s="190"/>
-      <c r="M95" s="190"/>
-      <c r="N95" s="190"/>
-      <c r="O95" s="190"/>
-      <c r="P95" s="190"/>
-    </row>
-    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="190"/>
-      <c r="E96" s="190"/>
-      <c r="F96" s="190"/>
-      <c r="G96" s="190"/>
-      <c r="H96" s="190"/>
-      <c r="I96" s="190"/>
-      <c r="J96" s="190"/>
-      <c r="K96" s="190"/>
-      <c r="L96" s="190"/>
-      <c r="M96" s="190"/>
-      <c r="N96" s="190"/>
-      <c r="O96" s="190"/>
-      <c r="P96" s="190"/>
-    </row>
-    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="190"/>
-      <c r="E97" s="190"/>
-      <c r="F97" s="190"/>
-      <c r="G97" s="190"/>
-      <c r="H97" s="190"/>
-      <c r="I97" s="190"/>
-      <c r="J97" s="190"/>
-      <c r="K97" s="190"/>
-      <c r="L97" s="190"/>
-      <c r="M97" s="190"/>
-      <c r="N97" s="190"/>
-      <c r="O97" s="190"/>
-      <c r="P97" s="190"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="190"/>
-      <c r="E98" s="190"/>
-      <c r="F98" s="190"/>
-      <c r="G98" s="190"/>
-      <c r="H98" s="190"/>
-      <c r="I98" s="190"/>
-      <c r="J98" s="190"/>
-      <c r="K98" s="190"/>
-      <c r="L98" s="190"/>
-      <c r="M98" s="190"/>
-      <c r="N98" s="190"/>
-      <c r="O98" s="190"/>
-      <c r="P98" s="190"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="190"/>
-      <c r="E99" s="190"/>
-      <c r="F99" s="190"/>
-      <c r="G99" s="190"/>
-      <c r="H99" s="190"/>
-      <c r="I99" s="190"/>
-      <c r="J99" s="190"/>
-      <c r="K99" s="190"/>
-      <c r="L99" s="190"/>
-      <c r="M99" s="190"/>
-      <c r="N99" s="190"/>
-      <c r="O99" s="190"/>
-      <c r="P99" s="190"/>
-    </row>
-    <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="190"/>
-      <c r="E100" s="190"/>
-      <c r="F100" s="190"/>
-      <c r="G100" s="190"/>
-      <c r="H100" s="190"/>
-      <c r="I100" s="190"/>
-      <c r="J100" s="190"/>
-      <c r="K100" s="190"/>
-      <c r="L100" s="190"/>
-      <c r="M100" s="190"/>
-      <c r="N100" s="190"/>
-      <c r="O100" s="190"/>
-      <c r="P100" s="190"/>
+      <c r="E95" s="194"/>
+      <c r="F95" s="194"/>
+      <c r="G95" s="194"/>
+      <c r="H95" s="194"/>
+      <c r="I95" s="194"/>
+      <c r="J95" s="194"/>
+      <c r="K95" s="194"/>
+      <c r="L95" s="194"/>
+      <c r="M95" s="194"/>
+      <c r="N95" s="194"/>
+      <c r="O95" s="194"/>
+      <c r="P95" s="194"/>
+    </row>
+    <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D96" s="194"/>
+      <c r="E96" s="194"/>
+      <c r="F96" s="194"/>
+      <c r="G96" s="194"/>
+      <c r="H96" s="194"/>
+      <c r="I96" s="194"/>
+      <c r="J96" s="194"/>
+      <c r="K96" s="194"/>
+      <c r="L96" s="194"/>
+      <c r="M96" s="194"/>
+      <c r="N96" s="194"/>
+      <c r="O96" s="194"/>
+      <c r="P96" s="194"/>
+    </row>
+    <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="194"/>
+      <c r="E97" s="194"/>
+      <c r="F97" s="194"/>
+      <c r="G97" s="194"/>
+      <c r="H97" s="194"/>
+      <c r="I97" s="194"/>
+      <c r="J97" s="194"/>
+      <c r="K97" s="194"/>
+      <c r="L97" s="194"/>
+      <c r="M97" s="194"/>
+      <c r="N97" s="194"/>
+      <c r="O97" s="194"/>
+      <c r="P97" s="194"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D98" s="194"/>
+      <c r="E98" s="194"/>
+      <c r="F98" s="194"/>
+      <c r="G98" s="194"/>
+      <c r="H98" s="194"/>
+      <c r="I98" s="194"/>
+      <c r="J98" s="194"/>
+      <c r="K98" s="194"/>
+      <c r="L98" s="194"/>
+      <c r="M98" s="194"/>
+      <c r="N98" s="194"/>
+      <c r="O98" s="194"/>
+      <c r="P98" s="194"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="194"/>
+      <c r="E99" s="194"/>
+      <c r="F99" s="194"/>
+      <c r="G99" s="194"/>
+      <c r="H99" s="194"/>
+      <c r="I99" s="194"/>
+      <c r="J99" s="194"/>
+      <c r="K99" s="194"/>
+      <c r="L99" s="194"/>
+      <c r="M99" s="194"/>
+      <c r="N99" s="194"/>
+      <c r="O99" s="194"/>
+      <c r="P99" s="194"/>
+    </row>
+    <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D100" s="194"/>
+      <c r="E100" s="194"/>
+      <c r="F100" s="194"/>
+      <c r="G100" s="194"/>
+      <c r="H100" s="194"/>
+      <c r="I100" s="194"/>
+      <c r="J100" s="194"/>
+      <c r="K100" s="194"/>
+      <c r="L100" s="194"/>
+      <c r="M100" s="194"/>
+      <c r="N100" s="194"/>
+      <c r="O100" s="194"/>
+      <c r="P100" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -9157,57 +9152,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
   <dimension ref="D3:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D3" s="120"/>
     </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D4" s="120"/>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D5" s="120"/>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D6" s="120"/>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D7" s="120"/>
     </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D8" s="120"/>
     </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D9" s="120"/>
     </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D10" s="120"/>
     </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D11" s="120"/>
     </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D12" s="120" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13" spans="4:4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D13" s="120"/>
     </row>
-    <row r="14" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D14" s="120"/>
     </row>
-    <row r="15" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D15" s="187" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D15" s="186" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="177" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D21" s="120"/>
       <c r="E21" s="120"/>
       <c r="F21" s="120"/>
